--- a/code/resultados/Exp_alpha0.5_NWJSSP_OADG_NEH(MS+ELS+SA).xlsx
+++ b/code/resultados/Exp_alpha0.5_NWJSSP_OADG_NEH(MS+ELS+SA).xlsx
@@ -19,6 +19,8 @@
     <sheet name="tai_j100_m10_1r" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="tai_j100_m100_1" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="tai_j100_m100_1r" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="tai_j1000_m10_1" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="tai_j1000_m10_1r" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1124,6 +1126,3354 @@
       <c r="B1" t="n">
         <v>3605236</v>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>121752</v>
+      </c>
+      <c r="B2" t="n">
+        <v>230611</v>
+      </c>
+      <c r="C2" t="n">
+        <v>425940</v>
+      </c>
+      <c r="D2" t="n">
+        <v>401557</v>
+      </c>
+      <c r="E2" t="n">
+        <v>791054</v>
+      </c>
+      <c r="F2" t="n">
+        <v>169900</v>
+      </c>
+      <c r="G2" t="n">
+        <v>446281</v>
+      </c>
+      <c r="H2" t="n">
+        <v>182093</v>
+      </c>
+      <c r="I2" t="n">
+        <v>807488</v>
+      </c>
+      <c r="J2" t="n">
+        <v>263204</v>
+      </c>
+      <c r="K2" t="n">
+        <v>466384</v>
+      </c>
+      <c r="L2" t="n">
+        <v>177692</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="N2" t="n">
+        <v>147106</v>
+      </c>
+      <c r="O2" t="n">
+        <v>106106</v>
+      </c>
+      <c r="P2" t="n">
+        <v>523286</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>696603</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>66513</v>
+      </c>
+      <c r="T2" t="n">
+        <v>493736</v>
+      </c>
+      <c r="U2" t="n">
+        <v>498060</v>
+      </c>
+      <c r="V2" t="n">
+        <v>702683</v>
+      </c>
+      <c r="W2" t="n">
+        <v>318992</v>
+      </c>
+      <c r="X2" t="n">
+        <v>473990</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>438896</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1217</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>827422</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>216963</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>604148</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>628088</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>590478</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>264531</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3191</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>651689</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>123821</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>756415</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>151078</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>134571</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>419978</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>65889</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>245814</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>561450</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>211130</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>265779</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>674552</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>657702</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>548595</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>746488</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>634557</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>167352</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>612978</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>408576</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>535285</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>376851</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>207166</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>213445</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>265494</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>347976</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>270864</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>511238</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>701989</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>493538</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>826157</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>293638</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>687641</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>322686</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>565668</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>608896</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>433421</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>35991</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>72557</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>145479</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>834416</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>359291</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>685487</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>51884</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>324818</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>478737</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>299733</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>534559</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>756327</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>578596</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>787333</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>194548</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>454946</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>324392</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>104268</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>575831</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>4199</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>373627</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>24396</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>89903</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>768552</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>386229</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>574356</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>115163</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>483919</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>633350</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>739421</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:ALL2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>581406932</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3659436</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>748793</v>
+      </c>
+      <c r="B2" t="n">
+        <v>445517</v>
+      </c>
+      <c r="C2" t="n">
+        <v>610297</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1146278</v>
+      </c>
+      <c r="E2" t="n">
+        <v>580641</v>
+      </c>
+      <c r="F2" t="n">
+        <v>941507</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1180578</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41887</v>
+      </c>
+      <c r="I2" t="n">
+        <v>458113</v>
+      </c>
+      <c r="J2" t="n">
+        <v>796125</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1152886</v>
+      </c>
+      <c r="L2" t="n">
+        <v>910673</v>
+      </c>
+      <c r="M2" t="n">
+        <v>343567</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1018068</v>
+      </c>
+      <c r="O2" t="n">
+        <v>876756</v>
+      </c>
+      <c r="P2" t="n">
+        <v>966202</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>623541</v>
+      </c>
+      <c r="R2" t="n">
+        <v>322036</v>
+      </c>
+      <c r="S2" t="n">
+        <v>915610</v>
+      </c>
+      <c r="T2" t="n">
+        <v>284174</v>
+      </c>
+      <c r="U2" t="n">
+        <v>834778</v>
+      </c>
+      <c r="V2" t="n">
+        <v>292832</v>
+      </c>
+      <c r="W2" t="n">
+        <v>80238</v>
+      </c>
+      <c r="X2" t="n">
+        <v>179980</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1104166</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>310098</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>110607</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>16539</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1150042</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>554116</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>289868</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1204977</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>372455</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>354639</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>308196</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>722699</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>537570</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1132534</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>518279</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>180916</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>366982</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>305197</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>18991</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>204</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>302848</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>594638</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>915671</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>23517</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>937742</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>279378</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>112728</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>18439</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>997952</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>999313</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>811838</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>467420</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>962917</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>868217</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>23085</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>316268</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1165802</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1053097</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>867308</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1167068</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>829393</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>8286</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>648532</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>999173</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>272552</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1143645</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>494330</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>344591</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>552094</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>12037</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1144505</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>114351</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>147511</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>817459</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>831944</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>163657</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>617222</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>731578</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>981005</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>396788</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>116742</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>387461</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>1024145</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>398446</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>299939</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>521869</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>266587</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>792192</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>748620</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>211768</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>602398</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>1108816</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>5827</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>178122</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>978921</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>696763</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>673682</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>175117</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>596974</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>754647</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>1185955</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1147497</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>738582</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>108645</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>423737</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>635496</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>169610</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>671581</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>401739</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>860214</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>1201931</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>245964</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>162374</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>735366</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>856562</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>385390</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>514173</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>954924</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1014653</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1048309</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1128619</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>745225</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>951706</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>659100</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>73218</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>869203</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>1064100</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>101989</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>837595</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>139183</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>1031136</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>408490</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>665923</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>1121011</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>577063</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>910204</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>321177</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>794640</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>1162192</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>1137220</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>689725</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>1048918</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>1097686</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>1002185</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>296364</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>69675</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>956791</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>394446</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>1006055</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>205518</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>1188121</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>775480</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>992905</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>888221</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>1031340</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>760297</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>590104</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>907764</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>843456</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>670596</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>527421</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>253226</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>1139156</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>839139</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>768936</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>485137</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>570180</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>385826</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>581678</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>444972</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>99961</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>740108</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>596152</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>1136346</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>505761</v>
+      </c>
+      <c r="FX2" t="n">
+        <v>782042</v>
+      </c>
+      <c r="FY2" t="n">
+        <v>963977</v>
+      </c>
+      <c r="FZ2" t="n">
+        <v>687931</v>
+      </c>
+      <c r="GA2" t="n">
+        <v>720884</v>
+      </c>
+      <c r="GB2" t="n">
+        <v>137898</v>
+      </c>
+      <c r="GC2" t="n">
+        <v>360692</v>
+      </c>
+      <c r="GD2" t="n">
+        <v>1032941</v>
+      </c>
+      <c r="GE2" t="n">
+        <v>775490</v>
+      </c>
+      <c r="GF2" t="n">
+        <v>638418</v>
+      </c>
+      <c r="GG2" t="n">
+        <v>1141011</v>
+      </c>
+      <c r="GH2" t="n">
+        <v>967414</v>
+      </c>
+      <c r="GI2" t="n">
+        <v>613674</v>
+      </c>
+      <c r="GJ2" t="n">
+        <v>352277</v>
+      </c>
+      <c r="GK2" t="n">
+        <v>989763</v>
+      </c>
+      <c r="GL2" t="n">
+        <v>968398</v>
+      </c>
+      <c r="GM2" t="n">
+        <v>886602</v>
+      </c>
+      <c r="GN2" t="n">
+        <v>679999</v>
+      </c>
+      <c r="GO2" t="n">
+        <v>10186</v>
+      </c>
+      <c r="GP2" t="n">
+        <v>771024</v>
+      </c>
+      <c r="GQ2" t="n">
+        <v>65522</v>
+      </c>
+      <c r="GR2" t="n">
+        <v>107481</v>
+      </c>
+      <c r="GS2" t="n">
+        <v>629500</v>
+      </c>
+      <c r="GT2" t="n">
+        <v>875618</v>
+      </c>
+      <c r="GU2" t="n">
+        <v>702340</v>
+      </c>
+      <c r="GV2" t="n">
+        <v>880067</v>
+      </c>
+      <c r="GW2" t="n">
+        <v>882573</v>
+      </c>
+      <c r="GX2" t="n">
+        <v>217182</v>
+      </c>
+      <c r="GY2" t="n">
+        <v>367129</v>
+      </c>
+      <c r="GZ2" t="n">
+        <v>58804</v>
+      </c>
+      <c r="HA2" t="n">
+        <v>1111287</v>
+      </c>
+      <c r="HB2" t="n">
+        <v>381717</v>
+      </c>
+      <c r="HC2" t="n">
+        <v>952902</v>
+      </c>
+      <c r="HD2" t="n">
+        <v>718301</v>
+      </c>
+      <c r="HE2" t="n">
+        <v>418060</v>
+      </c>
+      <c r="HF2" t="n">
+        <v>291155</v>
+      </c>
+      <c r="HG2" t="n">
+        <v>1023587</v>
+      </c>
+      <c r="HH2" t="n">
+        <v>902649</v>
+      </c>
+      <c r="HI2" t="n">
+        <v>134520</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>408337</v>
+      </c>
+      <c r="HK2" t="n">
+        <v>1003265</v>
+      </c>
+      <c r="HL2" t="n">
+        <v>855434</v>
+      </c>
+      <c r="HM2" t="n">
+        <v>89459</v>
+      </c>
+      <c r="HN2" t="n">
+        <v>607456</v>
+      </c>
+      <c r="HO2" t="n">
+        <v>171218</v>
+      </c>
+      <c r="HP2" t="n">
+        <v>125296</v>
+      </c>
+      <c r="HQ2" t="n">
+        <v>423582</v>
+      </c>
+      <c r="HR2" t="n">
+        <v>148890</v>
+      </c>
+      <c r="HS2" t="n">
+        <v>186695</v>
+      </c>
+      <c r="HT2" t="n">
+        <v>749279</v>
+      </c>
+      <c r="HU2" t="n">
+        <v>329821</v>
+      </c>
+      <c r="HV2" t="n">
+        <v>181836</v>
+      </c>
+      <c r="HW2" t="n">
+        <v>5654</v>
+      </c>
+      <c r="HX2" t="n">
+        <v>586042</v>
+      </c>
+      <c r="HY2" t="n">
+        <v>560275</v>
+      </c>
+      <c r="HZ2" t="n">
+        <v>955733</v>
+      </c>
+      <c r="IA2" t="n">
+        <v>125569</v>
+      </c>
+      <c r="IB2" t="n">
+        <v>164885</v>
+      </c>
+      <c r="IC2" t="n">
+        <v>489618</v>
+      </c>
+      <c r="ID2" t="n">
+        <v>755410</v>
+      </c>
+      <c r="IE2" t="n">
+        <v>939894</v>
+      </c>
+      <c r="IF2" t="n">
+        <v>153040</v>
+      </c>
+      <c r="IG2" t="n">
+        <v>1022269</v>
+      </c>
+      <c r="IH2" t="n">
+        <v>217058</v>
+      </c>
+      <c r="II2" t="n">
+        <v>65705</v>
+      </c>
+      <c r="IJ2" t="n">
+        <v>54158</v>
+      </c>
+      <c r="IK2" t="n">
+        <v>68260</v>
+      </c>
+      <c r="IL2" t="n">
+        <v>798903</v>
+      </c>
+      <c r="IM2" t="n">
+        <v>846073</v>
+      </c>
+      <c r="IN2" t="n">
+        <v>866448</v>
+      </c>
+      <c r="IO2" t="n">
+        <v>512322</v>
+      </c>
+      <c r="IP2" t="n">
+        <v>34643</v>
+      </c>
+      <c r="IQ2" t="n">
+        <v>947074</v>
+      </c>
+      <c r="IR2" t="n">
+        <v>428862</v>
+      </c>
+      <c r="IS2" t="n">
+        <v>991109</v>
+      </c>
+      <c r="IT2" t="n">
+        <v>105636</v>
+      </c>
+      <c r="IU2" t="n">
+        <v>459196</v>
+      </c>
+      <c r="IV2" t="n">
+        <v>798671</v>
+      </c>
+      <c r="IW2" t="n">
+        <v>331839</v>
+      </c>
+      <c r="IX2" t="n">
+        <v>419986</v>
+      </c>
+      <c r="IY2" t="n">
+        <v>903487</v>
+      </c>
+      <c r="IZ2" t="n">
+        <v>75703</v>
+      </c>
+      <c r="JA2" t="n">
+        <v>495999</v>
+      </c>
+      <c r="JB2" t="n">
+        <v>62085</v>
+      </c>
+      <c r="JC2" t="n">
+        <v>714770</v>
+      </c>
+      <c r="JD2" t="n">
+        <v>909964</v>
+      </c>
+      <c r="JE2" t="n">
+        <v>538171</v>
+      </c>
+      <c r="JF2" t="n">
+        <v>304057</v>
+      </c>
+      <c r="JG2" t="n">
+        <v>788017</v>
+      </c>
+      <c r="JH2" t="n">
+        <v>974537</v>
+      </c>
+      <c r="JI2" t="n">
+        <v>55827</v>
+      </c>
+      <c r="JJ2" t="n">
+        <v>545808</v>
+      </c>
+      <c r="JK2" t="n">
+        <v>1053761</v>
+      </c>
+      <c r="JL2" t="n">
+        <v>198050</v>
+      </c>
+      <c r="JM2" t="n">
+        <v>93594</v>
+      </c>
+      <c r="JN2" t="n">
+        <v>727725</v>
+      </c>
+      <c r="JO2" t="n">
+        <v>603481</v>
+      </c>
+      <c r="JP2" t="n">
+        <v>716117</v>
+      </c>
+      <c r="JQ2" t="n">
+        <v>895679</v>
+      </c>
+      <c r="JR2" t="n">
+        <v>136966</v>
+      </c>
+      <c r="JS2" t="n">
+        <v>310556</v>
+      </c>
+      <c r="JT2" t="n">
+        <v>255713</v>
+      </c>
+      <c r="JU2" t="n">
+        <v>1109654</v>
+      </c>
+      <c r="JV2" t="n">
+        <v>60518</v>
+      </c>
+      <c r="JW2" t="n">
+        <v>472773</v>
+      </c>
+      <c r="JX2" t="n">
+        <v>1089289</v>
+      </c>
+      <c r="JY2" t="n">
+        <v>172625</v>
+      </c>
+      <c r="JZ2" t="n">
+        <v>546403</v>
+      </c>
+      <c r="KA2" t="n">
+        <v>1068186</v>
+      </c>
+      <c r="KB2" t="n">
+        <v>822168</v>
+      </c>
+      <c r="KC2" t="n">
+        <v>147507</v>
+      </c>
+      <c r="KD2" t="n">
+        <v>323955</v>
+      </c>
+      <c r="KE2" t="n">
+        <v>195344</v>
+      </c>
+      <c r="KF2" t="n">
+        <v>665323</v>
+      </c>
+      <c r="KG2" t="n">
+        <v>150176</v>
+      </c>
+      <c r="KH2" t="n">
+        <v>163253</v>
+      </c>
+      <c r="KI2" t="n">
+        <v>1181645</v>
+      </c>
+      <c r="KJ2" t="n">
+        <v>1118627</v>
+      </c>
+      <c r="KK2" t="n">
+        <v>118281</v>
+      </c>
+      <c r="KL2" t="n">
+        <v>728726</v>
+      </c>
+      <c r="KM2" t="n">
+        <v>1127465</v>
+      </c>
+      <c r="KN2" t="n">
+        <v>153687</v>
+      </c>
+      <c r="KO2" t="n">
+        <v>918467</v>
+      </c>
+      <c r="KP2" t="n">
+        <v>40009</v>
+      </c>
+      <c r="KQ2" t="n">
+        <v>36708</v>
+      </c>
+      <c r="KR2" t="n">
+        <v>223307</v>
+      </c>
+      <c r="KS2" t="n">
+        <v>87973</v>
+      </c>
+      <c r="KT2" t="n">
+        <v>177168</v>
+      </c>
+      <c r="KU2" t="n">
+        <v>233244</v>
+      </c>
+      <c r="KV2" t="n">
+        <v>959347</v>
+      </c>
+      <c r="KW2" t="n">
+        <v>7538</v>
+      </c>
+      <c r="KX2" t="n">
+        <v>254069</v>
+      </c>
+      <c r="KY2" t="n">
+        <v>167445</v>
+      </c>
+      <c r="KZ2" t="n">
+        <v>414961</v>
+      </c>
+      <c r="LA2" t="n">
+        <v>278700</v>
+      </c>
+      <c r="LB2" t="n">
+        <v>1094419</v>
+      </c>
+      <c r="LC2" t="n">
+        <v>55562</v>
+      </c>
+      <c r="LD2" t="n">
+        <v>997259</v>
+      </c>
+      <c r="LE2" t="n">
+        <v>572022</v>
+      </c>
+      <c r="LF2" t="n">
+        <v>1077472</v>
+      </c>
+      <c r="LG2" t="n">
+        <v>587447</v>
+      </c>
+      <c r="LH2" t="n">
+        <v>232865</v>
+      </c>
+      <c r="LI2" t="n">
+        <v>784098</v>
+      </c>
+      <c r="LJ2" t="n">
+        <v>220879</v>
+      </c>
+      <c r="LK2" t="n">
+        <v>588568</v>
+      </c>
+      <c r="LL2" t="n">
+        <v>698335</v>
+      </c>
+      <c r="LM2" t="n">
+        <v>271815</v>
+      </c>
+      <c r="LN2" t="n">
+        <v>1041841</v>
+      </c>
+      <c r="LO2" t="n">
+        <v>483882</v>
+      </c>
+      <c r="LP2" t="n">
+        <v>1102647</v>
+      </c>
+      <c r="LQ2" t="n">
+        <v>563465</v>
+      </c>
+      <c r="LR2" t="n">
+        <v>704766</v>
+      </c>
+      <c r="LS2" t="n">
+        <v>224881</v>
+      </c>
+      <c r="LT2" t="n">
+        <v>543262</v>
+      </c>
+      <c r="LU2" t="n">
+        <v>550688</v>
+      </c>
+      <c r="LV2" t="n">
+        <v>1059017</v>
+      </c>
+      <c r="LW2" t="n">
+        <v>1062229</v>
+      </c>
+      <c r="LX2" t="n">
+        <v>1003646</v>
+      </c>
+      <c r="LY2" t="n">
+        <v>562290</v>
+      </c>
+      <c r="LZ2" t="n">
+        <v>207318</v>
+      </c>
+      <c r="MA2" t="n">
+        <v>465293</v>
+      </c>
+      <c r="MB2" t="n">
+        <v>665062</v>
+      </c>
+      <c r="MC2" t="n">
+        <v>121307</v>
+      </c>
+      <c r="MD2" t="n">
+        <v>1087502</v>
+      </c>
+      <c r="ME2" t="n">
+        <v>449026</v>
+      </c>
+      <c r="MF2" t="n">
+        <v>171728</v>
+      </c>
+      <c r="MG2" t="n">
+        <v>349532</v>
+      </c>
+      <c r="MH2" t="n">
+        <v>1126025</v>
+      </c>
+      <c r="MI2" t="n">
+        <v>234526</v>
+      </c>
+      <c r="MJ2" t="n">
+        <v>1092079</v>
+      </c>
+      <c r="MK2" t="n">
+        <v>612468</v>
+      </c>
+      <c r="ML2" t="n">
+        <v>143028</v>
+      </c>
+      <c r="MM2" t="n">
+        <v>114144</v>
+      </c>
+      <c r="MN2" t="n">
+        <v>1097521</v>
+      </c>
+      <c r="MO2" t="n">
+        <v>600796</v>
+      </c>
+      <c r="MP2" t="n">
+        <v>1106797</v>
+      </c>
+      <c r="MQ2" t="n">
+        <v>276446</v>
+      </c>
+      <c r="MR2" t="n">
+        <v>808321</v>
+      </c>
+      <c r="MS2" t="n">
+        <v>421084</v>
+      </c>
+      <c r="MT2" t="n">
+        <v>925541</v>
+      </c>
+      <c r="MU2" t="n">
+        <v>391013</v>
+      </c>
+      <c r="MV2" t="n">
+        <v>427628</v>
+      </c>
+      <c r="MW2" t="n">
+        <v>349038</v>
+      </c>
+      <c r="MX2" t="n">
+        <v>525059</v>
+      </c>
+      <c r="MY2" t="n">
+        <v>80112</v>
+      </c>
+      <c r="MZ2" t="n">
+        <v>438583</v>
+      </c>
+      <c r="NA2" t="n">
+        <v>737056</v>
+      </c>
+      <c r="NB2" t="n">
+        <v>154421</v>
+      </c>
+      <c r="NC2" t="n">
+        <v>333836</v>
+      </c>
+      <c r="ND2" t="n">
+        <v>676954</v>
+      </c>
+      <c r="NE2" t="n">
+        <v>858578</v>
+      </c>
+      <c r="NF2" t="n">
+        <v>1029563</v>
+      </c>
+      <c r="NG2" t="n">
+        <v>440531</v>
+      </c>
+      <c r="NH2" t="n">
+        <v>229818</v>
+      </c>
+      <c r="NI2" t="n">
+        <v>1156658</v>
+      </c>
+      <c r="NJ2" t="n">
+        <v>385979</v>
+      </c>
+      <c r="NK2" t="n">
+        <v>99151</v>
+      </c>
+      <c r="NL2" t="n">
+        <v>763617</v>
+      </c>
+      <c r="NM2" t="n">
+        <v>465582</v>
+      </c>
+      <c r="NN2" t="n">
+        <v>238882</v>
+      </c>
+      <c r="NO2" t="n">
+        <v>863843</v>
+      </c>
+      <c r="NP2" t="n">
+        <v>1188206</v>
+      </c>
+      <c r="NQ2" t="n">
+        <v>333680</v>
+      </c>
+      <c r="NR2" t="n">
+        <v>994543</v>
+      </c>
+      <c r="NS2" t="n">
+        <v>1159532</v>
+      </c>
+      <c r="NT2" t="n">
+        <v>511426</v>
+      </c>
+      <c r="NU2" t="n">
+        <v>323614</v>
+      </c>
+      <c r="NV2" t="n">
+        <v>944827</v>
+      </c>
+      <c r="NW2" t="n">
+        <v>3502</v>
+      </c>
+      <c r="NX2" t="n">
+        <v>4455</v>
+      </c>
+      <c r="NY2" t="n">
+        <v>556470</v>
+      </c>
+      <c r="NZ2" t="n">
+        <v>29435</v>
+      </c>
+      <c r="OA2" t="n">
+        <v>694758</v>
+      </c>
+      <c r="OB2" t="n">
+        <v>213041</v>
+      </c>
+      <c r="OC2" t="n">
+        <v>844377</v>
+      </c>
+      <c r="OD2" t="n">
+        <v>1037054</v>
+      </c>
+      <c r="OE2" t="n">
+        <v>1168373</v>
+      </c>
+      <c r="OF2" t="n">
+        <v>261864</v>
+      </c>
+      <c r="OG2" t="n">
+        <v>13063</v>
+      </c>
+      <c r="OH2" t="n">
+        <v>919830</v>
+      </c>
+      <c r="OI2" t="n">
+        <v>1067852</v>
+      </c>
+      <c r="OJ2" t="n">
+        <v>901410</v>
+      </c>
+      <c r="OK2" t="n">
+        <v>825507</v>
+      </c>
+      <c r="OL2" t="n">
+        <v>723689</v>
+      </c>
+      <c r="OM2" t="n">
+        <v>50319</v>
+      </c>
+      <c r="ON2" t="n">
+        <v>1092124</v>
+      </c>
+      <c r="OO2" t="n">
+        <v>687075</v>
+      </c>
+      <c r="OP2" t="n">
+        <v>1186014</v>
+      </c>
+      <c r="OQ2" t="n">
+        <v>1043559</v>
+      </c>
+      <c r="OR2" t="n">
+        <v>628631</v>
+      </c>
+      <c r="OS2" t="n">
+        <v>294462</v>
+      </c>
+      <c r="OT2" t="n">
+        <v>416984</v>
+      </c>
+      <c r="OU2" t="n">
+        <v>854533</v>
+      </c>
+      <c r="OV2" t="n">
+        <v>250813</v>
+      </c>
+      <c r="OW2" t="n">
+        <v>700421</v>
+      </c>
+      <c r="OX2" t="n">
+        <v>469989</v>
+      </c>
+      <c r="OY2" t="n">
+        <v>223922</v>
+      </c>
+      <c r="OZ2" t="n">
+        <v>826225</v>
+      </c>
+      <c r="PA2" t="n">
+        <v>734786</v>
+      </c>
+      <c r="PB2" t="n">
+        <v>872798</v>
+      </c>
+      <c r="PC2" t="n">
+        <v>1089395</v>
+      </c>
+      <c r="PD2" t="n">
+        <v>45478</v>
+      </c>
+      <c r="PE2" t="n">
+        <v>420877</v>
+      </c>
+      <c r="PF2" t="n">
+        <v>829239</v>
+      </c>
+      <c r="PG2" t="n">
+        <v>911719</v>
+      </c>
+      <c r="PH2" t="n">
+        <v>808843</v>
+      </c>
+      <c r="PI2" t="n">
+        <v>1000973</v>
+      </c>
+      <c r="PJ2" t="n">
+        <v>647073</v>
+      </c>
+      <c r="PK2" t="n">
+        <v>23212</v>
+      </c>
+      <c r="PL2" t="n">
+        <v>486552</v>
+      </c>
+      <c r="PM2" t="n">
+        <v>1197539</v>
+      </c>
+      <c r="PN2" t="n">
+        <v>1876</v>
+      </c>
+      <c r="PO2" t="n">
+        <v>205835</v>
+      </c>
+      <c r="PP2" t="n">
+        <v>729225</v>
+      </c>
+      <c r="PQ2" t="n">
+        <v>623564</v>
+      </c>
+      <c r="PR2" t="n">
+        <v>656401</v>
+      </c>
+      <c r="PS2" t="n">
+        <v>495294</v>
+      </c>
+      <c r="PT2" t="n">
+        <v>693137</v>
+      </c>
+      <c r="PU2" t="n">
+        <v>534404</v>
+      </c>
+      <c r="PV2" t="n">
+        <v>345044</v>
+      </c>
+      <c r="PW2" t="n">
+        <v>328416</v>
+      </c>
+      <c r="PX2" t="n">
+        <v>85149</v>
+      </c>
+      <c r="PY2" t="n">
+        <v>239268</v>
+      </c>
+      <c r="PZ2" t="n">
+        <v>642423</v>
+      </c>
+      <c r="QA2" t="n">
+        <v>1007219</v>
+      </c>
+      <c r="QB2" t="n">
+        <v>38584</v>
+      </c>
+      <c r="QC2" t="n">
+        <v>471162</v>
+      </c>
+      <c r="QD2" t="n">
+        <v>490768</v>
+      </c>
+      <c r="QE2" t="n">
+        <v>717007</v>
+      </c>
+      <c r="QF2" t="n">
+        <v>34325</v>
+      </c>
+      <c r="QG2" t="n">
+        <v>979720</v>
+      </c>
+      <c r="QH2" t="n">
+        <v>645544</v>
+      </c>
+      <c r="QI2" t="n">
+        <v>875428</v>
+      </c>
+      <c r="QJ2" t="n">
+        <v>548577</v>
+      </c>
+      <c r="QK2" t="n">
+        <v>222353</v>
+      </c>
+      <c r="QL2" t="n">
+        <v>883900</v>
+      </c>
+      <c r="QM2" t="n">
+        <v>615532</v>
+      </c>
+      <c r="QN2" t="n">
+        <v>690678</v>
+      </c>
+      <c r="QO2" t="n">
+        <v>11955</v>
+      </c>
+      <c r="QP2" t="n">
+        <v>209256</v>
+      </c>
+      <c r="QQ2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="QR2" t="n">
+        <v>381972</v>
+      </c>
+      <c r="QS2" t="n">
+        <v>591772</v>
+      </c>
+      <c r="QT2" t="n">
+        <v>437125</v>
+      </c>
+      <c r="QU2" t="n">
+        <v>1128357</v>
+      </c>
+      <c r="QV2" t="n">
+        <v>374540</v>
+      </c>
+      <c r="QW2" t="n">
+        <v>774424</v>
+      </c>
+      <c r="QX2" t="n">
+        <v>839103</v>
+      </c>
+      <c r="QY2" t="n">
+        <v>772492</v>
+      </c>
+      <c r="QZ2" t="n">
+        <v>554512</v>
+      </c>
+      <c r="RA2" t="n">
+        <v>450315</v>
+      </c>
+      <c r="RB2" t="n">
+        <v>931686</v>
+      </c>
+      <c r="RC2" t="n">
+        <v>779411</v>
+      </c>
+      <c r="RD2" t="n">
+        <v>174415</v>
+      </c>
+      <c r="RE2" t="n">
+        <v>622158</v>
+      </c>
+      <c r="RF2" t="n">
+        <v>30472</v>
+      </c>
+      <c r="RG2" t="n">
+        <v>452037</v>
+      </c>
+      <c r="RH2" t="n">
+        <v>790580</v>
+      </c>
+      <c r="RI2" t="n">
+        <v>620804</v>
+      </c>
+      <c r="RJ2" t="n">
+        <v>1055446</v>
+      </c>
+      <c r="RK2" t="n">
+        <v>431288</v>
+      </c>
+      <c r="RL2" t="n">
+        <v>599078</v>
+      </c>
+      <c r="RM2" t="n">
+        <v>398360</v>
+      </c>
+      <c r="RN2" t="n">
+        <v>529938</v>
+      </c>
+      <c r="RO2" t="n">
+        <v>156257</v>
+      </c>
+      <c r="RP2" t="n">
+        <v>709455</v>
+      </c>
+      <c r="RQ2" t="n">
+        <v>820253</v>
+      </c>
+      <c r="RR2" t="n">
+        <v>1011897</v>
+      </c>
+      <c r="RS2" t="n">
+        <v>342331</v>
+      </c>
+      <c r="RT2" t="n">
+        <v>158105</v>
+      </c>
+      <c r="RU2" t="n">
+        <v>531809</v>
+      </c>
+      <c r="RV2" t="n">
+        <v>898967</v>
+      </c>
+      <c r="RW2" t="n">
+        <v>542455</v>
+      </c>
+      <c r="RX2" t="n">
+        <v>978111</v>
+      </c>
+      <c r="RY2" t="n">
+        <v>630823</v>
+      </c>
+      <c r="RZ2" t="n">
+        <v>303828</v>
+      </c>
+      <c r="SA2" t="n">
+        <v>320350</v>
+      </c>
+      <c r="SB2" t="n">
+        <v>283285</v>
+      </c>
+      <c r="SC2" t="n">
+        <v>48359</v>
+      </c>
+      <c r="SD2" t="n">
+        <v>110153</v>
+      </c>
+      <c r="SE2" t="n">
+        <v>264452</v>
+      </c>
+      <c r="SF2" t="n">
+        <v>357745</v>
+      </c>
+      <c r="SG2" t="n">
+        <v>143823</v>
+      </c>
+      <c r="SH2" t="n">
+        <v>1208924</v>
+      </c>
+      <c r="SI2" t="n">
+        <v>1123447</v>
+      </c>
+      <c r="SJ2" t="n">
+        <v>405371</v>
+      </c>
+      <c r="SK2" t="n">
+        <v>307328</v>
+      </c>
+      <c r="SL2" t="n">
+        <v>669739</v>
+      </c>
+      <c r="SM2" t="n">
+        <v>537768</v>
+      </c>
+      <c r="SN2" t="n">
+        <v>787808</v>
+      </c>
+      <c r="SO2" t="n">
+        <v>991805</v>
+      </c>
+      <c r="SP2" t="n">
+        <v>259359</v>
+      </c>
+      <c r="SQ2" t="n">
+        <v>387727</v>
+      </c>
+      <c r="SR2" t="n">
+        <v>1184943</v>
+      </c>
+      <c r="SS2" t="n">
+        <v>834674</v>
+      </c>
+      <c r="ST2" t="n">
+        <v>764405</v>
+      </c>
+      <c r="SU2" t="n">
+        <v>804121</v>
+      </c>
+      <c r="SV2" t="n">
+        <v>813392</v>
+      </c>
+      <c r="SW2" t="n">
+        <v>492159</v>
+      </c>
+      <c r="SX2" t="n">
+        <v>810742</v>
+      </c>
+      <c r="SY2" t="n">
+        <v>568950</v>
+      </c>
+      <c r="SZ2" t="n">
+        <v>1056987</v>
+      </c>
+      <c r="TA2" t="n">
+        <v>504852</v>
+      </c>
+      <c r="TB2" t="n">
+        <v>854673</v>
+      </c>
+      <c r="TC2" t="n">
+        <v>125742</v>
+      </c>
+      <c r="TD2" t="n">
+        <v>753425</v>
+      </c>
+      <c r="TE2" t="n">
+        <v>402496</v>
+      </c>
+      <c r="TF2" t="n">
+        <v>933223</v>
+      </c>
+      <c r="TG2" t="n">
+        <v>885500</v>
+      </c>
+      <c r="TH2" t="n">
+        <v>1075585</v>
+      </c>
+      <c r="TI2" t="n">
+        <v>227485</v>
+      </c>
+      <c r="TJ2" t="n">
+        <v>508140</v>
+      </c>
+      <c r="TK2" t="n">
+        <v>203530</v>
+      </c>
+      <c r="TL2" t="n">
+        <v>84414</v>
+      </c>
+      <c r="TM2" t="n">
+        <v>322828</v>
+      </c>
+      <c r="TN2" t="n">
+        <v>20850</v>
+      </c>
+      <c r="TO2" t="n">
+        <v>482008</v>
+      </c>
+      <c r="TP2" t="n">
+        <v>859952</v>
+      </c>
+      <c r="TQ2" t="n">
+        <v>202609</v>
+      </c>
+      <c r="TR2" t="n">
+        <v>98447</v>
+      </c>
+      <c r="TS2" t="n">
+        <v>479027</v>
+      </c>
+      <c r="TT2" t="n">
+        <v>567524</v>
+      </c>
+      <c r="TU2" t="n">
+        <v>1153624</v>
+      </c>
+      <c r="TV2" t="n">
+        <v>1055764</v>
+      </c>
+      <c r="TW2" t="n">
+        <v>1161540</v>
+      </c>
+      <c r="TX2" t="n">
+        <v>92923</v>
+      </c>
+      <c r="TY2" t="n">
+        <v>534029</v>
+      </c>
+      <c r="TZ2" t="n">
+        <v>1133457</v>
+      </c>
+      <c r="UA2" t="n">
+        <v>334146</v>
+      </c>
+      <c r="UB2" t="n">
+        <v>1023976</v>
+      </c>
+      <c r="UC2" t="n">
+        <v>1122210</v>
+      </c>
+      <c r="UD2" t="n">
+        <v>1019615</v>
+      </c>
+      <c r="UE2" t="n">
+        <v>535564</v>
+      </c>
+      <c r="UF2" t="n">
+        <v>129371</v>
+      </c>
+      <c r="UG2" t="n">
+        <v>349331</v>
+      </c>
+      <c r="UH2" t="n">
+        <v>1051014</v>
+      </c>
+      <c r="UI2" t="n">
+        <v>609967</v>
+      </c>
+      <c r="UJ2" t="n">
+        <v>633067</v>
+      </c>
+      <c r="UK2" t="n">
+        <v>822285</v>
+      </c>
+      <c r="UL2" t="n">
+        <v>132568</v>
+      </c>
+      <c r="UM2" t="n">
+        <v>741435</v>
+      </c>
+      <c r="UN2" t="n">
+        <v>574786</v>
+      </c>
+      <c r="UO2" t="n">
+        <v>709922</v>
+      </c>
+      <c r="UP2" t="n">
+        <v>178596</v>
+      </c>
+      <c r="UQ2" t="n">
+        <v>471129</v>
+      </c>
+      <c r="UR2" t="n">
+        <v>1080365</v>
+      </c>
+      <c r="US2" t="n">
+        <v>801718</v>
+      </c>
+      <c r="UT2" t="n">
+        <v>865325</v>
+      </c>
+      <c r="UU2" t="n">
+        <v>239643</v>
+      </c>
+      <c r="UV2" t="n">
+        <v>410101</v>
+      </c>
+      <c r="UW2" t="n">
+        <v>930313</v>
+      </c>
+      <c r="UX2" t="n">
+        <v>994527</v>
+      </c>
+      <c r="UY2" t="n">
+        <v>924639</v>
+      </c>
+      <c r="UZ2" t="n">
+        <v>639660</v>
+      </c>
+      <c r="VA2" t="n">
+        <v>104314</v>
+      </c>
+      <c r="VB2" t="n">
+        <v>724419</v>
+      </c>
+      <c r="VC2" t="n">
+        <v>541265</v>
+      </c>
+      <c r="VD2" t="n">
+        <v>346784</v>
+      </c>
+      <c r="VE2" t="n">
+        <v>580148</v>
+      </c>
+      <c r="VF2" t="n">
+        <v>87093</v>
+      </c>
+      <c r="VG2" t="n">
+        <v>579073</v>
+      </c>
+      <c r="VH2" t="n">
+        <v>317991</v>
+      </c>
+      <c r="VI2" t="n">
+        <v>305037</v>
+      </c>
+      <c r="VJ2" t="n">
+        <v>913463</v>
+      </c>
+      <c r="VK2" t="n">
+        <v>260308</v>
+      </c>
+      <c r="VL2" t="n">
+        <v>1066214</v>
+      </c>
+      <c r="VM2" t="n">
+        <v>285837</v>
+      </c>
+      <c r="VN2" t="n">
+        <v>161556</v>
+      </c>
+      <c r="VO2" t="n">
+        <v>933359</v>
+      </c>
+      <c r="VP2" t="n">
+        <v>517459</v>
+      </c>
+      <c r="VQ2" t="n">
+        <v>830991</v>
+      </c>
+      <c r="VR2" t="n">
+        <v>793071</v>
+      </c>
+      <c r="VS2" t="n">
+        <v>455066</v>
+      </c>
+      <c r="VT2" t="n">
+        <v>1070733</v>
+      </c>
+      <c r="VU2" t="n">
+        <v>565106</v>
+      </c>
+      <c r="VV2" t="n">
+        <v>897482</v>
+      </c>
+      <c r="VW2" t="n">
+        <v>786333</v>
+      </c>
+      <c r="VX2" t="n">
+        <v>514829</v>
+      </c>
+      <c r="VY2" t="n">
+        <v>853258</v>
+      </c>
+      <c r="VZ2" t="n">
+        <v>46729</v>
+      </c>
+      <c r="WA2" t="n">
+        <v>103257</v>
+      </c>
+      <c r="WB2" t="n">
+        <v>790461</v>
+      </c>
+      <c r="WC2" t="n">
+        <v>146719</v>
+      </c>
+      <c r="WD2" t="n">
+        <v>70541</v>
+      </c>
+      <c r="WE2" t="n">
+        <v>85981</v>
+      </c>
+      <c r="WF2" t="n">
+        <v>200302</v>
+      </c>
+      <c r="WG2" t="n">
+        <v>740657</v>
+      </c>
+      <c r="WH2" t="n">
+        <v>246554</v>
+      </c>
+      <c r="WI2" t="n">
+        <v>374426</v>
+      </c>
+      <c r="WJ2" t="n">
+        <v>697424</v>
+      </c>
+      <c r="WK2" t="n">
+        <v>1085001</v>
+      </c>
+      <c r="WL2" t="n">
+        <v>84611</v>
+      </c>
+      <c r="WM2" t="n">
+        <v>194134</v>
+      </c>
+      <c r="WN2" t="n">
+        <v>16381</v>
+      </c>
+      <c r="WO2" t="n">
+        <v>666900</v>
+      </c>
+      <c r="WP2" t="n">
+        <v>2430</v>
+      </c>
+      <c r="WQ2" t="n">
+        <v>1106599</v>
+      </c>
+      <c r="WR2" t="n">
+        <v>1027728</v>
+      </c>
+      <c r="WS2" t="n">
+        <v>547481</v>
+      </c>
+      <c r="WT2" t="n">
+        <v>74861</v>
+      </c>
+      <c r="WU2" t="n">
+        <v>295533</v>
+      </c>
+      <c r="WV2" t="n">
+        <v>500290</v>
+      </c>
+      <c r="WW2" t="n">
+        <v>393965</v>
+      </c>
+      <c r="WX2" t="n">
+        <v>434828</v>
+      </c>
+      <c r="WY2" t="n">
+        <v>1016210</v>
+      </c>
+      <c r="WZ2" t="n">
+        <v>336341</v>
+      </c>
+      <c r="XA2" t="n">
+        <v>462798</v>
+      </c>
+      <c r="XB2" t="n">
+        <v>922118</v>
+      </c>
+      <c r="XC2" t="n">
+        <v>225679</v>
+      </c>
+      <c r="XD2" t="n">
+        <v>118623</v>
+      </c>
+      <c r="XE2" t="n">
+        <v>33195</v>
+      </c>
+      <c r="XF2" t="n">
+        <v>500838</v>
+      </c>
+      <c r="XG2" t="n">
+        <v>453404</v>
+      </c>
+      <c r="XH2" t="n">
+        <v>63492</v>
+      </c>
+      <c r="XI2" t="n">
+        <v>1080452</v>
+      </c>
+      <c r="XJ2" t="n">
+        <v>970946</v>
+      </c>
+      <c r="XK2" t="n">
+        <v>74890</v>
+      </c>
+      <c r="XL2" t="n">
+        <v>824227</v>
+      </c>
+      <c r="XM2" t="n">
+        <v>510507</v>
+      </c>
+      <c r="XN2" t="n">
+        <v>598861</v>
+      </c>
+      <c r="XO2" t="n">
+        <v>873067</v>
+      </c>
+      <c r="XP2" t="n">
+        <v>950571</v>
+      </c>
+      <c r="XQ2" t="n">
+        <v>704621</v>
+      </c>
+      <c r="XR2" t="n">
+        <v>779810</v>
+      </c>
+      <c r="XS2" t="n">
+        <v>1047216</v>
+      </c>
+      <c r="XT2" t="n">
+        <v>566643</v>
+      </c>
+      <c r="XU2" t="n">
+        <v>805290</v>
+      </c>
+      <c r="XV2" t="n">
+        <v>890967</v>
+      </c>
+      <c r="XW2" t="n">
+        <v>1170904</v>
+      </c>
+      <c r="XX2" t="n">
+        <v>235483</v>
+      </c>
+      <c r="XY2" t="n">
+        <v>848708</v>
+      </c>
+      <c r="XZ2" t="n">
+        <v>14119</v>
+      </c>
+      <c r="YA2" t="n">
+        <v>265569</v>
+      </c>
+      <c r="YB2" t="n">
+        <v>189152</v>
+      </c>
+      <c r="YC2" t="n">
+        <v>667365</v>
+      </c>
+      <c r="YD2" t="n">
+        <v>421626</v>
+      </c>
+      <c r="YE2" t="n">
+        <v>15309</v>
+      </c>
+      <c r="YF2" t="n">
+        <v>848234</v>
+      </c>
+      <c r="YG2" t="n">
+        <v>49199</v>
+      </c>
+      <c r="YH2" t="n">
+        <v>503336</v>
+      </c>
+      <c r="YI2" t="n">
+        <v>355131</v>
+      </c>
+      <c r="YJ2" t="n">
+        <v>877020</v>
+      </c>
+      <c r="YK2" t="n">
+        <v>905794</v>
+      </c>
+      <c r="YL2" t="n">
+        <v>1115369</v>
+      </c>
+      <c r="YM2" t="n">
+        <v>569899</v>
+      </c>
+      <c r="YN2" t="n">
+        <v>10262</v>
+      </c>
+      <c r="YO2" t="n">
+        <v>977464</v>
+      </c>
+      <c r="YP2" t="n">
+        <v>685974</v>
+      </c>
+      <c r="YQ2" t="n">
+        <v>598900</v>
+      </c>
+      <c r="YR2" t="n">
+        <v>509038</v>
+      </c>
+      <c r="YS2" t="n">
+        <v>726380</v>
+      </c>
+      <c r="YT2" t="n">
+        <v>842493</v>
+      </c>
+      <c r="YU2" t="n">
+        <v>81188</v>
+      </c>
+      <c r="YV2" t="n">
+        <v>262898</v>
+      </c>
+      <c r="YW2" t="n">
+        <v>1020981</v>
+      </c>
+      <c r="YX2" t="n">
+        <v>1119166</v>
+      </c>
+      <c r="YY2" t="n">
+        <v>649659</v>
+      </c>
+      <c r="YZ2" t="n">
+        <v>786702</v>
+      </c>
+      <c r="ZA2" t="n">
+        <v>290341</v>
+      </c>
+      <c r="ZB2" t="n">
+        <v>917624</v>
+      </c>
+      <c r="ZC2" t="n">
+        <v>370374</v>
+      </c>
+      <c r="ZD2" t="n">
+        <v>1200780</v>
+      </c>
+      <c r="ZE2" t="n">
+        <v>26340</v>
+      </c>
+      <c r="ZF2" t="n">
+        <v>65718</v>
+      </c>
+      <c r="ZG2" t="n">
+        <v>37858</v>
+      </c>
+      <c r="ZH2" t="n">
+        <v>184213</v>
+      </c>
+      <c r="ZI2" t="n">
+        <v>71203</v>
+      </c>
+      <c r="ZJ2" t="n">
+        <v>226718</v>
+      </c>
+      <c r="ZK2" t="n">
+        <v>78806</v>
+      </c>
+      <c r="ZL2" t="n">
+        <v>963896</v>
+      </c>
+      <c r="ZM2" t="n">
+        <v>880933</v>
+      </c>
+      <c r="ZN2" t="n">
+        <v>923720</v>
+      </c>
+      <c r="ZO2" t="n">
+        <v>430597</v>
+      </c>
+      <c r="ZP2" t="n">
+        <v>317133</v>
+      </c>
+      <c r="ZQ2" t="n">
+        <v>803447</v>
+      </c>
+      <c r="ZR2" t="n">
+        <v>763525</v>
+      </c>
+      <c r="ZS2" t="n">
+        <v>337216</v>
+      </c>
+      <c r="ZT2" t="n">
+        <v>249321</v>
+      </c>
+      <c r="ZU2" t="n">
+        <v>1150598</v>
+      </c>
+      <c r="ZV2" t="n">
+        <v>197153</v>
+      </c>
+      <c r="ZW2" t="n">
+        <v>19487</v>
+      </c>
+      <c r="ZX2" t="n">
+        <v>340452</v>
+      </c>
+      <c r="ZY2" t="n">
+        <v>414835</v>
+      </c>
+      <c r="ZZ2" t="n">
+        <v>1167297</v>
+      </c>
+      <c r="AAA2" t="n">
+        <v>949724</v>
+      </c>
+      <c r="AAB2" t="n">
+        <v>441351</v>
+      </c>
+      <c r="AAC2" t="n">
+        <v>443898</v>
+      </c>
+      <c r="AAD2" t="n">
+        <v>1041653</v>
+      </c>
+      <c r="AAE2" t="n">
+        <v>616255</v>
+      </c>
+      <c r="AAF2" t="n">
+        <v>862481</v>
+      </c>
+      <c r="AAG2" t="n">
+        <v>840205</v>
+      </c>
+      <c r="AAH2" t="n">
+        <v>182767</v>
+      </c>
+      <c r="AAI2" t="n">
+        <v>759074</v>
+      </c>
+      <c r="AAJ2" t="n">
+        <v>985216</v>
+      </c>
+      <c r="AAK2" t="n">
+        <v>746643</v>
+      </c>
+      <c r="AAL2" t="n">
+        <v>141805</v>
+      </c>
+      <c r="AAM2" t="n">
+        <v>359132</v>
+      </c>
+      <c r="AAN2" t="n">
+        <v>1014438</v>
+      </c>
+      <c r="AAO2" t="n">
+        <v>366034</v>
+      </c>
+      <c r="AAP2" t="n">
+        <v>410598</v>
+      </c>
+      <c r="AAQ2" t="n">
+        <v>949575</v>
+      </c>
+      <c r="AAR2" t="n">
+        <v>1214488</v>
+      </c>
+      <c r="AAS2" t="n">
+        <v>95722</v>
+      </c>
+      <c r="AAT2" t="n">
+        <v>608270</v>
+      </c>
+      <c r="AAU2" t="n">
+        <v>167127</v>
+      </c>
+      <c r="AAV2" t="n">
+        <v>27511</v>
+      </c>
+      <c r="AAW2" t="n">
+        <v>814473</v>
+      </c>
+      <c r="AAX2" t="n">
+        <v>906619</v>
+      </c>
+      <c r="AAY2" t="n">
+        <v>1043394</v>
+      </c>
+      <c r="AAZ2" t="n">
+        <v>56508</v>
+      </c>
+      <c r="ABA2" t="n">
+        <v>27769</v>
+      </c>
+      <c r="ABB2" t="n">
+        <v>218372</v>
+      </c>
+      <c r="ABC2" t="n">
+        <v>960300</v>
+      </c>
+      <c r="ABD2" t="n">
+        <v>460818</v>
+      </c>
+      <c r="ABE2" t="n">
+        <v>776344</v>
+      </c>
+      <c r="ABF2" t="n">
+        <v>1033834</v>
+      </c>
+      <c r="ABG2" t="n">
+        <v>487034</v>
+      </c>
+      <c r="ABH2" t="n">
+        <v>516899</v>
+      </c>
+      <c r="ABI2" t="n">
+        <v>314144</v>
+      </c>
+      <c r="ABJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ABK2" t="n">
+        <v>1036472</v>
+      </c>
+      <c r="ABL2" t="n">
+        <v>848792</v>
+      </c>
+      <c r="ABM2" t="n">
+        <v>112737</v>
+      </c>
+      <c r="ABN2" t="n">
+        <v>799406</v>
+      </c>
+      <c r="ABO2" t="n">
+        <v>14692</v>
+      </c>
+      <c r="ABP2" t="n">
+        <v>338710</v>
+      </c>
+      <c r="ABQ2" t="n">
+        <v>360258</v>
+      </c>
+      <c r="ABR2" t="n">
+        <v>502552</v>
+      </c>
+      <c r="ABS2" t="n">
+        <v>1198754</v>
+      </c>
+      <c r="ABT2" t="n">
+        <v>427011</v>
+      </c>
+      <c r="ABU2" t="n">
+        <v>314136</v>
+      </c>
+      <c r="ABV2" t="n">
+        <v>1045830</v>
+      </c>
+      <c r="ABW2" t="n">
+        <v>650418</v>
+      </c>
+      <c r="ABX2" t="n">
+        <v>455665</v>
+      </c>
+      <c r="ABY2" t="n">
+        <v>120731</v>
+      </c>
+      <c r="ABZ2" t="n">
+        <v>482437</v>
+      </c>
+      <c r="ACA2" t="n">
+        <v>79294</v>
+      </c>
+      <c r="ACB2" t="n">
+        <v>21949</v>
+      </c>
+      <c r="ACC2" t="n">
+        <v>297430</v>
+      </c>
+      <c r="ACD2" t="n">
+        <v>101019</v>
+      </c>
+      <c r="ACE2" t="n">
+        <v>128173</v>
+      </c>
+      <c r="ACF2" t="n">
+        <v>656742</v>
+      </c>
+      <c r="ACG2" t="n">
+        <v>808684</v>
+      </c>
+      <c r="ACH2" t="n">
+        <v>1012908</v>
+      </c>
+      <c r="ACI2" t="n">
+        <v>59717</v>
+      </c>
+      <c r="ACJ2" t="n">
+        <v>641686</v>
+      </c>
+      <c r="ACK2" t="n">
+        <v>1081212</v>
+      </c>
+      <c r="ACL2" t="n">
+        <v>1156549</v>
+      </c>
+      <c r="ACM2" t="n">
+        <v>1134957</v>
+      </c>
+      <c r="ACN2" t="n">
+        <v>214773</v>
+      </c>
+      <c r="ACO2" t="n">
+        <v>1093959</v>
+      </c>
+      <c r="ACP2" t="n">
+        <v>582362</v>
+      </c>
+      <c r="ACQ2" t="n">
+        <v>894776</v>
+      </c>
+      <c r="ACR2" t="n">
+        <v>426182</v>
+      </c>
+      <c r="ACS2" t="n">
+        <v>469217</v>
+      </c>
+      <c r="ACT2" t="n">
+        <v>460881</v>
+      </c>
+      <c r="ACU2" t="n">
+        <v>692017</v>
+      </c>
+      <c r="ACV2" t="n">
+        <v>583429</v>
+      </c>
+      <c r="ACW2" t="n">
+        <v>890520</v>
+      </c>
+      <c r="ACX2" t="n">
+        <v>487179</v>
+      </c>
+      <c r="ACY2" t="n">
+        <v>1113444</v>
+      </c>
+      <c r="ACZ2" t="n">
+        <v>378001</v>
+      </c>
+      <c r="ADA2" t="n">
+        <v>936631</v>
+      </c>
+      <c r="ADB2" t="n">
+        <v>356503</v>
+      </c>
+      <c r="ADC2" t="n">
+        <v>736104</v>
+      </c>
+      <c r="ADD2" t="n">
+        <v>556984</v>
+      </c>
+      <c r="ADE2" t="n">
+        <v>620711</v>
+      </c>
+      <c r="ADF2" t="n">
+        <v>44064</v>
+      </c>
+      <c r="ADG2" t="n">
+        <v>212001</v>
+      </c>
+      <c r="ADH2" t="n">
+        <v>263582</v>
+      </c>
+      <c r="ADI2" t="n">
+        <v>257355</v>
+      </c>
+      <c r="ADJ2" t="n">
+        <v>521771</v>
+      </c>
+      <c r="ADK2" t="n">
+        <v>1039823</v>
+      </c>
+      <c r="ADL2" t="n">
+        <v>298626</v>
+      </c>
+      <c r="ADM2" t="n">
+        <v>680921</v>
+      </c>
+      <c r="ADN2" t="n">
+        <v>1174219</v>
+      </c>
+      <c r="ADO2" t="n">
+        <v>1193255</v>
+      </c>
+      <c r="ADP2" t="n">
+        <v>267314</v>
+      </c>
+      <c r="ADQ2" t="n">
+        <v>157804</v>
+      </c>
+      <c r="ADR2" t="n">
+        <v>747739</v>
+      </c>
+      <c r="ADS2" t="n">
+        <v>209847</v>
+      </c>
+      <c r="ADT2" t="n">
+        <v>958020</v>
+      </c>
+      <c r="ADU2" t="n">
+        <v>653106</v>
+      </c>
+      <c r="ADV2" t="n">
+        <v>686381</v>
+      </c>
+      <c r="ADW2" t="n">
+        <v>411644</v>
+      </c>
+      <c r="ADX2" t="n">
+        <v>944426</v>
+      </c>
+      <c r="ADY2" t="n">
+        <v>465795</v>
+      </c>
+      <c r="ADZ2" t="n">
+        <v>1161483</v>
+      </c>
+      <c r="AEA2" t="n">
+        <v>653376</v>
+      </c>
+      <c r="AEB2" t="n">
+        <v>450545</v>
+      </c>
+      <c r="AEC2" t="n">
+        <v>52374</v>
+      </c>
+      <c r="AED2" t="n">
+        <v>474601</v>
+      </c>
+      <c r="AEE2" t="n">
+        <v>634113</v>
+      </c>
+      <c r="AEF2" t="n">
+        <v>230525</v>
+      </c>
+      <c r="AEG2" t="n">
+        <v>506086</v>
+      </c>
+      <c r="AEH2" t="n">
+        <v>433608</v>
+      </c>
+      <c r="AEI2" t="n">
+        <v>31372</v>
+      </c>
+      <c r="AEJ2" t="n">
+        <v>1027867</v>
+      </c>
+      <c r="AEK2" t="n">
+        <v>681716</v>
+      </c>
+      <c r="AEL2" t="n">
+        <v>193366</v>
+      </c>
+      <c r="AEM2" t="n">
+        <v>1208695</v>
+      </c>
+      <c r="AEN2" t="n">
+        <v>751918</v>
+      </c>
+      <c r="AEO2" t="n">
+        <v>287287</v>
+      </c>
+      <c r="AEP2" t="n">
+        <v>561253</v>
+      </c>
+      <c r="AEQ2" t="n">
+        <v>851877</v>
+      </c>
+      <c r="AER2" t="n">
+        <v>91323</v>
+      </c>
+      <c r="AES2" t="n">
+        <v>40403</v>
+      </c>
+      <c r="AET2" t="n">
+        <v>712672</v>
+      </c>
+      <c r="AEU2" t="n">
+        <v>662204</v>
+      </c>
+      <c r="AEV2" t="n">
+        <v>130218</v>
+      </c>
+      <c r="AEW2" t="n">
+        <v>390639</v>
+      </c>
+      <c r="AEX2" t="n">
+        <v>539593</v>
+      </c>
+      <c r="AEY2" t="n">
+        <v>328215</v>
+      </c>
+      <c r="AEZ2" t="n">
+        <v>554974</v>
+      </c>
+      <c r="AFA2" t="n">
+        <v>711382</v>
+      </c>
+      <c r="AFB2" t="n">
+        <v>382781</v>
+      </c>
+      <c r="AFC2" t="n">
+        <v>370386</v>
+      </c>
+      <c r="AFD2" t="n">
+        <v>592898</v>
+      </c>
+      <c r="AFE2" t="n">
+        <v>134757</v>
+      </c>
+      <c r="AFF2" t="n">
+        <v>730454</v>
+      </c>
+      <c r="AFG2" t="n">
+        <v>757338</v>
+      </c>
+      <c r="AFH2" t="n">
+        <v>892158</v>
+      </c>
+      <c r="AFI2" t="n">
+        <v>1172365</v>
+      </c>
+      <c r="AFJ2" t="n">
+        <v>278584</v>
+      </c>
+      <c r="AFK2" t="n">
+        <v>968898</v>
+      </c>
+      <c r="AFL2" t="n">
+        <v>192244</v>
+      </c>
+      <c r="AFM2" t="n">
+        <v>527057</v>
+      </c>
+      <c r="AFN2" t="n">
+        <v>404480</v>
+      </c>
+      <c r="AFO2" t="n">
+        <v>973152</v>
+      </c>
+      <c r="AFP2" t="n">
+        <v>1009274</v>
+      </c>
+      <c r="AFQ2" t="n">
+        <v>459733</v>
+      </c>
+      <c r="AFR2" t="n">
+        <v>768056</v>
+      </c>
+      <c r="AFS2" t="n">
+        <v>832952</v>
+      </c>
+      <c r="AFT2" t="n">
+        <v>637937</v>
+      </c>
+      <c r="AFU2" t="n">
+        <v>68007</v>
+      </c>
+      <c r="AFV2" t="n">
+        <v>393808</v>
+      </c>
+      <c r="AFW2" t="n">
+        <v>1025280</v>
+      </c>
+      <c r="AFX2" t="n">
+        <v>352021</v>
+      </c>
+      <c r="AFY2" t="n">
+        <v>1196405</v>
+      </c>
+      <c r="AFZ2" t="n">
+        <v>712941</v>
+      </c>
+      <c r="AGA2" t="n">
+        <v>1078913</v>
+      </c>
+      <c r="AGB2" t="n">
+        <v>269317</v>
+      </c>
+      <c r="AGC2" t="n">
+        <v>325621</v>
+      </c>
+      <c r="AGD2" t="n">
+        <v>1010335</v>
+      </c>
+      <c r="AGE2" t="n">
+        <v>453199</v>
+      </c>
+      <c r="AGF2" t="n">
+        <v>1203178</v>
+      </c>
+      <c r="AGG2" t="n">
+        <v>1176703</v>
+      </c>
+      <c r="AGH2" t="n">
+        <v>124445</v>
+      </c>
+      <c r="AGI2" t="n">
+        <v>400565</v>
+      </c>
+      <c r="AGJ2" t="n">
+        <v>520313</v>
+      </c>
+      <c r="AGK2" t="n">
+        <v>989373</v>
+      </c>
+      <c r="AGL2" t="n">
+        <v>824717</v>
+      </c>
+      <c r="AGM2" t="n">
+        <v>402127</v>
+      </c>
+      <c r="AGN2" t="n">
+        <v>936179</v>
+      </c>
+      <c r="AGO2" t="n">
+        <v>879175</v>
+      </c>
+      <c r="AGP2" t="n">
+        <v>326544</v>
+      </c>
+      <c r="AGQ2" t="n">
+        <v>25230</v>
+      </c>
+      <c r="AGR2" t="n">
+        <v>1209390</v>
+      </c>
+      <c r="AGS2" t="n">
+        <v>742835</v>
+      </c>
+      <c r="AGT2" t="n">
+        <v>141022</v>
+      </c>
+      <c r="AGU2" t="n">
+        <v>958959</v>
+      </c>
+      <c r="AGV2" t="n">
+        <v>886352</v>
+      </c>
+      <c r="AGW2" t="n">
+        <v>96113</v>
+      </c>
+      <c r="AGX2" t="n">
+        <v>628888</v>
+      </c>
+      <c r="AGY2" t="n">
+        <v>242153</v>
+      </c>
+      <c r="AGZ2" t="n">
+        <v>243104</v>
+      </c>
+      <c r="AHA2" t="n">
+        <v>129883</v>
+      </c>
+      <c r="AHB2" t="n">
+        <v>214</v>
+      </c>
+      <c r="AHC2" t="n">
+        <v>1151257</v>
+      </c>
+      <c r="AHD2" t="n">
+        <v>672889</v>
+      </c>
+      <c r="AHE2" t="n">
+        <v>292763</v>
+      </c>
+      <c r="AHF2" t="n">
+        <v>159492</v>
+      </c>
+      <c r="AHG2" t="n">
+        <v>185924</v>
+      </c>
+      <c r="AHH2" t="n">
+        <v>605206</v>
+      </c>
+      <c r="AHI2" t="n">
+        <v>987347</v>
+      </c>
+      <c r="AHJ2" t="n">
+        <v>253507</v>
+      </c>
+      <c r="AHK2" t="n">
+        <v>308949</v>
+      </c>
+      <c r="AHL2" t="n">
+        <v>340020</v>
+      </c>
+      <c r="AHM2" t="n">
+        <v>41859</v>
+      </c>
+      <c r="AHN2" t="n">
+        <v>929964</v>
+      </c>
+      <c r="AHO2" t="n">
+        <v>942972</v>
+      </c>
+      <c r="AHP2" t="n">
+        <v>643412</v>
+      </c>
+      <c r="AHQ2" t="n">
+        <v>153198</v>
+      </c>
+      <c r="AHR2" t="n">
+        <v>363264</v>
+      </c>
+      <c r="AHS2" t="n">
+        <v>585555</v>
+      </c>
+      <c r="AHT2" t="n">
+        <v>258781</v>
+      </c>
+      <c r="AHU2" t="n">
+        <v>819195</v>
+      </c>
+      <c r="AHV2" t="n">
+        <v>8862</v>
+      </c>
+      <c r="AHW2" t="n">
+        <v>237291</v>
+      </c>
+      <c r="AHX2" t="n">
+        <v>6643</v>
+      </c>
+      <c r="AHY2" t="n">
+        <v>441000</v>
+      </c>
+      <c r="AHZ2" t="n">
+        <v>138812</v>
+      </c>
+      <c r="AIA2" t="n">
+        <v>804214</v>
+      </c>
+      <c r="AIB2" t="n">
+        <v>1179474</v>
+      </c>
+      <c r="AIC2" t="n">
+        <v>733103</v>
+      </c>
+      <c r="AID2" t="n">
+        <v>1084639</v>
+      </c>
+      <c r="AIE2" t="n">
+        <v>557710</v>
+      </c>
+      <c r="AIF2" t="n">
+        <v>376415</v>
+      </c>
+      <c r="AIG2" t="n">
+        <v>706703</v>
+      </c>
+      <c r="AIH2" t="n">
+        <v>1061169</v>
+      </c>
+      <c r="AII2" t="n">
+        <v>1100105</v>
+      </c>
+      <c r="AIJ2" t="n">
+        <v>1131776</v>
+      </c>
+      <c r="AIK2" t="n">
+        <v>427097</v>
+      </c>
+      <c r="AIL2" t="n">
+        <v>329954</v>
+      </c>
+      <c r="AIM2" t="n">
+        <v>233925</v>
+      </c>
+      <c r="AIN2" t="n">
+        <v>719935</v>
+      </c>
+      <c r="AIO2" t="n">
+        <v>92919</v>
+      </c>
+      <c r="AIP2" t="n">
+        <v>542387</v>
+      </c>
+      <c r="AIQ2" t="n">
+        <v>1073545</v>
+      </c>
+      <c r="AIR2" t="n">
+        <v>436510</v>
+      </c>
+      <c r="AIS2" t="n">
+        <v>707067</v>
+      </c>
+      <c r="AIT2" t="n">
+        <v>656077</v>
+      </c>
+      <c r="AIU2" t="n">
+        <v>921081</v>
+      </c>
+      <c r="AIV2" t="n">
+        <v>61571</v>
+      </c>
+      <c r="AIW2" t="n">
+        <v>44408</v>
+      </c>
+      <c r="AIX2" t="n">
+        <v>1139778</v>
+      </c>
+      <c r="AIY2" t="n">
+        <v>984388</v>
+      </c>
+      <c r="AIZ2" t="n">
+        <v>816508</v>
+      </c>
+      <c r="AJA2" t="n">
+        <v>1038409</v>
+      </c>
+      <c r="AJB2" t="n">
+        <v>456226</v>
+      </c>
+      <c r="AJC2" t="n">
+        <v>445204</v>
+      </c>
+      <c r="AJD2" t="n">
+        <v>286646</v>
+      </c>
+      <c r="AJE2" t="n">
+        <v>412481</v>
+      </c>
+      <c r="AJF2" t="n">
+        <v>766442</v>
+      </c>
+      <c r="AJG2" t="n">
+        <v>1190649</v>
+      </c>
+      <c r="AJH2" t="n">
+        <v>197283</v>
+      </c>
+      <c r="AJI2" t="n">
+        <v>500828</v>
+      </c>
+      <c r="AJJ2" t="n">
+        <v>477982</v>
+      </c>
+      <c r="AJK2" t="n">
+        <v>77042</v>
+      </c>
+      <c r="AJL2" t="n">
+        <v>274493</v>
+      </c>
+      <c r="AJM2" t="n">
+        <v>650944</v>
+      </c>
+      <c r="AJN2" t="n">
+        <v>1075915</v>
+      </c>
+      <c r="AJO2" t="n">
+        <v>476467</v>
+      </c>
+      <c r="AJP2" t="n">
+        <v>274396</v>
+      </c>
+      <c r="AJQ2" t="n">
+        <v>782122</v>
+      </c>
+      <c r="AJR2" t="n">
+        <v>89201</v>
+      </c>
+      <c r="AJS2" t="n">
+        <v>192751</v>
+      </c>
+      <c r="AJT2" t="n">
+        <v>29414</v>
+      </c>
+      <c r="AJU2" t="n">
+        <v>770566</v>
+      </c>
+      <c r="AJV2" t="n">
+        <v>1102060</v>
+      </c>
+      <c r="AJW2" t="n">
+        <v>134234</v>
+      </c>
+      <c r="AJX2" t="n">
+        <v>531421</v>
+      </c>
+      <c r="AJY2" t="n">
+        <v>1072175</v>
+      </c>
+      <c r="AJZ2" t="n">
+        <v>532459</v>
+      </c>
+      <c r="AKA2" t="n">
+        <v>574982</v>
+      </c>
+      <c r="AKB2" t="n">
+        <v>1116575</v>
+      </c>
+      <c r="AKC2" t="n">
+        <v>497703</v>
+      </c>
+      <c r="AKD2" t="n">
+        <v>618645</v>
+      </c>
+      <c r="AKE2" t="n">
+        <v>982915</v>
+      </c>
+      <c r="AKF2" t="n">
+        <v>973665</v>
+      </c>
+      <c r="AKG2" t="n">
+        <v>837085</v>
+      </c>
+      <c r="AKH2" t="n">
+        <v>625176</v>
+      </c>
+      <c r="AKI2" t="n">
+        <v>673704</v>
+      </c>
+      <c r="AKJ2" t="n">
+        <v>1124708</v>
+      </c>
+      <c r="AKK2" t="n">
+        <v>705351</v>
+      </c>
+      <c r="AKL2" t="n">
+        <v>218873</v>
+      </c>
+      <c r="AKM2" t="n">
+        <v>564180</v>
+      </c>
+      <c r="AKN2" t="n">
+        <v>281728</v>
+      </c>
+      <c r="AKO2" t="n">
+        <v>476892</v>
+      </c>
+      <c r="AKP2" t="n">
+        <v>660412</v>
+      </c>
+      <c r="AKQ2" t="n">
+        <v>928632</v>
+      </c>
+      <c r="AKR2" t="n">
+        <v>938726</v>
+      </c>
+      <c r="AKS2" t="n">
+        <v>249044</v>
+      </c>
+      <c r="AKT2" t="n">
+        <v>1173628</v>
+      </c>
+      <c r="AKU2" t="n">
+        <v>398038</v>
+      </c>
+      <c r="AKV2" t="n">
+        <v>362204</v>
+      </c>
+      <c r="AKW2" t="n">
+        <v>5038</v>
+      </c>
+      <c r="AKX2" t="n">
+        <v>575819</v>
+      </c>
+      <c r="AKY2" t="n">
+        <v>218365</v>
+      </c>
+      <c r="AKZ2" t="n">
+        <v>680586</v>
+      </c>
+      <c r="ALA2" t="n">
+        <v>449236</v>
+      </c>
+      <c r="ALB2" t="n">
+        <v>684288</v>
+      </c>
+      <c r="ALC2" t="n">
+        <v>188144</v>
+      </c>
+      <c r="ALD2" t="n">
+        <v>50583</v>
+      </c>
+      <c r="ALE2" t="n">
+        <v>243108</v>
+      </c>
+      <c r="ALF2" t="n">
+        <v>661208</v>
+      </c>
+      <c r="ALG2" t="n">
+        <v>677298</v>
+      </c>
+      <c r="ALH2" t="n">
+        <v>893342</v>
+      </c>
+      <c r="ALI2" t="n">
+        <v>245527</v>
+      </c>
+      <c r="ALJ2" t="n">
+        <v>644671</v>
+      </c>
+      <c r="ALK2" t="n">
+        <v>900622</v>
+      </c>
+      <c r="ALL2" t="n">
+        <v>1009268</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:ALL2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>581209135</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3639126</v>
+      </c>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr"/>
@@ -1222,307 +4572,3907 @@
       <c r="CT1" t="inlineStr"/>
       <c r="CU1" t="inlineStr"/>
       <c r="CV1" t="inlineStr"/>
+      <c r="CW1" t="inlineStr"/>
+      <c r="CX1" t="inlineStr"/>
+      <c r="CY1" t="inlineStr"/>
+      <c r="CZ1" t="inlineStr"/>
+      <c r="DA1" t="inlineStr"/>
+      <c r="DB1" t="inlineStr"/>
+      <c r="DC1" t="inlineStr"/>
+      <c r="DD1" t="inlineStr"/>
+      <c r="DE1" t="inlineStr"/>
+      <c r="DF1" t="inlineStr"/>
+      <c r="DG1" t="inlineStr"/>
+      <c r="DH1" t="inlineStr"/>
+      <c r="DI1" t="inlineStr"/>
+      <c r="DJ1" t="inlineStr"/>
+      <c r="DK1" t="inlineStr"/>
+      <c r="DL1" t="inlineStr"/>
+      <c r="DM1" t="inlineStr"/>
+      <c r="DN1" t="inlineStr"/>
+      <c r="DO1" t="inlineStr"/>
+      <c r="DP1" t="inlineStr"/>
+      <c r="DQ1" t="inlineStr"/>
+      <c r="DR1" t="inlineStr"/>
+      <c r="DS1" t="inlineStr"/>
+      <c r="DT1" t="inlineStr"/>
+      <c r="DU1" t="inlineStr"/>
+      <c r="DV1" t="inlineStr"/>
+      <c r="DW1" t="inlineStr"/>
+      <c r="DX1" t="inlineStr"/>
+      <c r="DY1" t="inlineStr"/>
+      <c r="DZ1" t="inlineStr"/>
+      <c r="EA1" t="inlineStr"/>
+      <c r="EB1" t="inlineStr"/>
+      <c r="EC1" t="inlineStr"/>
+      <c r="ED1" t="inlineStr"/>
+      <c r="EE1" t="inlineStr"/>
+      <c r="EF1" t="inlineStr"/>
+      <c r="EG1" t="inlineStr"/>
+      <c r="EH1" t="inlineStr"/>
+      <c r="EI1" t="inlineStr"/>
+      <c r="EJ1" t="inlineStr"/>
+      <c r="EK1" t="inlineStr"/>
+      <c r="EL1" t="inlineStr"/>
+      <c r="EM1" t="inlineStr"/>
+      <c r="EN1" t="inlineStr"/>
+      <c r="EO1" t="inlineStr"/>
+      <c r="EP1" t="inlineStr"/>
+      <c r="EQ1" t="inlineStr"/>
+      <c r="ER1" t="inlineStr"/>
+      <c r="ES1" t="inlineStr"/>
+      <c r="ET1" t="inlineStr"/>
+      <c r="EU1" t="inlineStr"/>
+      <c r="EV1" t="inlineStr"/>
+      <c r="EW1" t="inlineStr"/>
+      <c r="EX1" t="inlineStr"/>
+      <c r="EY1" t="inlineStr"/>
+      <c r="EZ1" t="inlineStr"/>
+      <c r="FA1" t="inlineStr"/>
+      <c r="FB1" t="inlineStr"/>
+      <c r="FC1" t="inlineStr"/>
+      <c r="FD1" t="inlineStr"/>
+      <c r="FE1" t="inlineStr"/>
+      <c r="FF1" t="inlineStr"/>
+      <c r="FG1" t="inlineStr"/>
+      <c r="FH1" t="inlineStr"/>
+      <c r="FI1" t="inlineStr"/>
+      <c r="FJ1" t="inlineStr"/>
+      <c r="FK1" t="inlineStr"/>
+      <c r="FL1" t="inlineStr"/>
+      <c r="FM1" t="inlineStr"/>
+      <c r="FN1" t="inlineStr"/>
+      <c r="FO1" t="inlineStr"/>
+      <c r="FP1" t="inlineStr"/>
+      <c r="FQ1" t="inlineStr"/>
+      <c r="FR1" t="inlineStr"/>
+      <c r="FS1" t="inlineStr"/>
+      <c r="FT1" t="inlineStr"/>
+      <c r="FU1" t="inlineStr"/>
+      <c r="FV1" t="inlineStr"/>
+      <c r="FW1" t="inlineStr"/>
+      <c r="FX1" t="inlineStr"/>
+      <c r="FY1" t="inlineStr"/>
+      <c r="FZ1" t="inlineStr"/>
+      <c r="GA1" t="inlineStr"/>
+      <c r="GB1" t="inlineStr"/>
+      <c r="GC1" t="inlineStr"/>
+      <c r="GD1" t="inlineStr"/>
+      <c r="GE1" t="inlineStr"/>
+      <c r="GF1" t="inlineStr"/>
+      <c r="GG1" t="inlineStr"/>
+      <c r="GH1" t="inlineStr"/>
+      <c r="GI1" t="inlineStr"/>
+      <c r="GJ1" t="inlineStr"/>
+      <c r="GK1" t="inlineStr"/>
+      <c r="GL1" t="inlineStr"/>
+      <c r="GM1" t="inlineStr"/>
+      <c r="GN1" t="inlineStr"/>
+      <c r="GO1" t="inlineStr"/>
+      <c r="GP1" t="inlineStr"/>
+      <c r="GQ1" t="inlineStr"/>
+      <c r="GR1" t="inlineStr"/>
+      <c r="GS1" t="inlineStr"/>
+      <c r="GT1" t="inlineStr"/>
+      <c r="GU1" t="inlineStr"/>
+      <c r="GV1" t="inlineStr"/>
+      <c r="GW1" t="inlineStr"/>
+      <c r="GX1" t="inlineStr"/>
+      <c r="GY1" t="inlineStr"/>
+      <c r="GZ1" t="inlineStr"/>
+      <c r="HA1" t="inlineStr"/>
+      <c r="HB1" t="inlineStr"/>
+      <c r="HC1" t="inlineStr"/>
+      <c r="HD1" t="inlineStr"/>
+      <c r="HE1" t="inlineStr"/>
+      <c r="HF1" t="inlineStr"/>
+      <c r="HG1" t="inlineStr"/>
+      <c r="HH1" t="inlineStr"/>
+      <c r="HI1" t="inlineStr"/>
+      <c r="HJ1" t="inlineStr"/>
+      <c r="HK1" t="inlineStr"/>
+      <c r="HL1" t="inlineStr"/>
+      <c r="HM1" t="inlineStr"/>
+      <c r="HN1" t="inlineStr"/>
+      <c r="HO1" t="inlineStr"/>
+      <c r="HP1" t="inlineStr"/>
+      <c r="HQ1" t="inlineStr"/>
+      <c r="HR1" t="inlineStr"/>
+      <c r="HS1" t="inlineStr"/>
+      <c r="HT1" t="inlineStr"/>
+      <c r="HU1" t="inlineStr"/>
+      <c r="HV1" t="inlineStr"/>
+      <c r="HW1" t="inlineStr"/>
+      <c r="HX1" t="inlineStr"/>
+      <c r="HY1" t="inlineStr"/>
+      <c r="HZ1" t="inlineStr"/>
+      <c r="IA1" t="inlineStr"/>
+      <c r="IB1" t="inlineStr"/>
+      <c r="IC1" t="inlineStr"/>
+      <c r="ID1" t="inlineStr"/>
+      <c r="IE1" t="inlineStr"/>
+      <c r="IF1" t="inlineStr"/>
+      <c r="IG1" t="inlineStr"/>
+      <c r="IH1" t="inlineStr"/>
+      <c r="II1" t="inlineStr"/>
+      <c r="IJ1" t="inlineStr"/>
+      <c r="IK1" t="inlineStr"/>
+      <c r="IL1" t="inlineStr"/>
+      <c r="IM1" t="inlineStr"/>
+      <c r="IN1" t="inlineStr"/>
+      <c r="IO1" t="inlineStr"/>
+      <c r="IP1" t="inlineStr"/>
+      <c r="IQ1" t="inlineStr"/>
+      <c r="IR1" t="inlineStr"/>
+      <c r="IS1" t="inlineStr"/>
+      <c r="IT1" t="inlineStr"/>
+      <c r="IU1" t="inlineStr"/>
+      <c r="IV1" t="inlineStr"/>
+      <c r="IW1" t="inlineStr"/>
+      <c r="IX1" t="inlineStr"/>
+      <c r="IY1" t="inlineStr"/>
+      <c r="IZ1" t="inlineStr"/>
+      <c r="JA1" t="inlineStr"/>
+      <c r="JB1" t="inlineStr"/>
+      <c r="JC1" t="inlineStr"/>
+      <c r="JD1" t="inlineStr"/>
+      <c r="JE1" t="inlineStr"/>
+      <c r="JF1" t="inlineStr"/>
+      <c r="JG1" t="inlineStr"/>
+      <c r="JH1" t="inlineStr"/>
+      <c r="JI1" t="inlineStr"/>
+      <c r="JJ1" t="inlineStr"/>
+      <c r="JK1" t="inlineStr"/>
+      <c r="JL1" t="inlineStr"/>
+      <c r="JM1" t="inlineStr"/>
+      <c r="JN1" t="inlineStr"/>
+      <c r="JO1" t="inlineStr"/>
+      <c r="JP1" t="inlineStr"/>
+      <c r="JQ1" t="inlineStr"/>
+      <c r="JR1" t="inlineStr"/>
+      <c r="JS1" t="inlineStr"/>
+      <c r="JT1" t="inlineStr"/>
+      <c r="JU1" t="inlineStr"/>
+      <c r="JV1" t="inlineStr"/>
+      <c r="JW1" t="inlineStr"/>
+      <c r="JX1" t="inlineStr"/>
+      <c r="JY1" t="inlineStr"/>
+      <c r="JZ1" t="inlineStr"/>
+      <c r="KA1" t="inlineStr"/>
+      <c r="KB1" t="inlineStr"/>
+      <c r="KC1" t="inlineStr"/>
+      <c r="KD1" t="inlineStr"/>
+      <c r="KE1" t="inlineStr"/>
+      <c r="KF1" t="inlineStr"/>
+      <c r="KG1" t="inlineStr"/>
+      <c r="KH1" t="inlineStr"/>
+      <c r="KI1" t="inlineStr"/>
+      <c r="KJ1" t="inlineStr"/>
+      <c r="KK1" t="inlineStr"/>
+      <c r="KL1" t="inlineStr"/>
+      <c r="KM1" t="inlineStr"/>
+      <c r="KN1" t="inlineStr"/>
+      <c r="KO1" t="inlineStr"/>
+      <c r="KP1" t="inlineStr"/>
+      <c r="KQ1" t="inlineStr"/>
+      <c r="KR1" t="inlineStr"/>
+      <c r="KS1" t="inlineStr"/>
+      <c r="KT1" t="inlineStr"/>
+      <c r="KU1" t="inlineStr"/>
+      <c r="KV1" t="inlineStr"/>
+      <c r="KW1" t="inlineStr"/>
+      <c r="KX1" t="inlineStr"/>
+      <c r="KY1" t="inlineStr"/>
+      <c r="KZ1" t="inlineStr"/>
+      <c r="LA1" t="inlineStr"/>
+      <c r="LB1" t="inlineStr"/>
+      <c r="LC1" t="inlineStr"/>
+      <c r="LD1" t="inlineStr"/>
+      <c r="LE1" t="inlineStr"/>
+      <c r="LF1" t="inlineStr"/>
+      <c r="LG1" t="inlineStr"/>
+      <c r="LH1" t="inlineStr"/>
+      <c r="LI1" t="inlineStr"/>
+      <c r="LJ1" t="inlineStr"/>
+      <c r="LK1" t="inlineStr"/>
+      <c r="LL1" t="inlineStr"/>
+      <c r="LM1" t="inlineStr"/>
+      <c r="LN1" t="inlineStr"/>
+      <c r="LO1" t="inlineStr"/>
+      <c r="LP1" t="inlineStr"/>
+      <c r="LQ1" t="inlineStr"/>
+      <c r="LR1" t="inlineStr"/>
+      <c r="LS1" t="inlineStr"/>
+      <c r="LT1" t="inlineStr"/>
+      <c r="LU1" t="inlineStr"/>
+      <c r="LV1" t="inlineStr"/>
+      <c r="LW1" t="inlineStr"/>
+      <c r="LX1" t="inlineStr"/>
+      <c r="LY1" t="inlineStr"/>
+      <c r="LZ1" t="inlineStr"/>
+      <c r="MA1" t="inlineStr"/>
+      <c r="MB1" t="inlineStr"/>
+      <c r="MC1" t="inlineStr"/>
+      <c r="MD1" t="inlineStr"/>
+      <c r="ME1" t="inlineStr"/>
+      <c r="MF1" t="inlineStr"/>
+      <c r="MG1" t="inlineStr"/>
+      <c r="MH1" t="inlineStr"/>
+      <c r="MI1" t="inlineStr"/>
+      <c r="MJ1" t="inlineStr"/>
+      <c r="MK1" t="inlineStr"/>
+      <c r="ML1" t="inlineStr"/>
+      <c r="MM1" t="inlineStr"/>
+      <c r="MN1" t="inlineStr"/>
+      <c r="MO1" t="inlineStr"/>
+      <c r="MP1" t="inlineStr"/>
+      <c r="MQ1" t="inlineStr"/>
+      <c r="MR1" t="inlineStr"/>
+      <c r="MS1" t="inlineStr"/>
+      <c r="MT1" t="inlineStr"/>
+      <c r="MU1" t="inlineStr"/>
+      <c r="MV1" t="inlineStr"/>
+      <c r="MW1" t="inlineStr"/>
+      <c r="MX1" t="inlineStr"/>
+      <c r="MY1" t="inlineStr"/>
+      <c r="MZ1" t="inlineStr"/>
+      <c r="NA1" t="inlineStr"/>
+      <c r="NB1" t="inlineStr"/>
+      <c r="NC1" t="inlineStr"/>
+      <c r="ND1" t="inlineStr"/>
+      <c r="NE1" t="inlineStr"/>
+      <c r="NF1" t="inlineStr"/>
+      <c r="NG1" t="inlineStr"/>
+      <c r="NH1" t="inlineStr"/>
+      <c r="NI1" t="inlineStr"/>
+      <c r="NJ1" t="inlineStr"/>
+      <c r="NK1" t="inlineStr"/>
+      <c r="NL1" t="inlineStr"/>
+      <c r="NM1" t="inlineStr"/>
+      <c r="NN1" t="inlineStr"/>
+      <c r="NO1" t="inlineStr"/>
+      <c r="NP1" t="inlineStr"/>
+      <c r="NQ1" t="inlineStr"/>
+      <c r="NR1" t="inlineStr"/>
+      <c r="NS1" t="inlineStr"/>
+      <c r="NT1" t="inlineStr"/>
+      <c r="NU1" t="inlineStr"/>
+      <c r="NV1" t="inlineStr"/>
+      <c r="NW1" t="inlineStr"/>
+      <c r="NX1" t="inlineStr"/>
+      <c r="NY1" t="inlineStr"/>
+      <c r="NZ1" t="inlineStr"/>
+      <c r="OA1" t="inlineStr"/>
+      <c r="OB1" t="inlineStr"/>
+      <c r="OC1" t="inlineStr"/>
+      <c r="OD1" t="inlineStr"/>
+      <c r="OE1" t="inlineStr"/>
+      <c r="OF1" t="inlineStr"/>
+      <c r="OG1" t="inlineStr"/>
+      <c r="OH1" t="inlineStr"/>
+      <c r="OI1" t="inlineStr"/>
+      <c r="OJ1" t="inlineStr"/>
+      <c r="OK1" t="inlineStr"/>
+      <c r="OL1" t="inlineStr"/>
+      <c r="OM1" t="inlineStr"/>
+      <c r="ON1" t="inlineStr"/>
+      <c r="OO1" t="inlineStr"/>
+      <c r="OP1" t="inlineStr"/>
+      <c r="OQ1" t="inlineStr"/>
+      <c r="OR1" t="inlineStr"/>
+      <c r="OS1" t="inlineStr"/>
+      <c r="OT1" t="inlineStr"/>
+      <c r="OU1" t="inlineStr"/>
+      <c r="OV1" t="inlineStr"/>
+      <c r="OW1" t="inlineStr"/>
+      <c r="OX1" t="inlineStr"/>
+      <c r="OY1" t="inlineStr"/>
+      <c r="OZ1" t="inlineStr"/>
+      <c r="PA1" t="inlineStr"/>
+      <c r="PB1" t="inlineStr"/>
+      <c r="PC1" t="inlineStr"/>
+      <c r="PD1" t="inlineStr"/>
+      <c r="PE1" t="inlineStr"/>
+      <c r="PF1" t="inlineStr"/>
+      <c r="PG1" t="inlineStr"/>
+      <c r="PH1" t="inlineStr"/>
+      <c r="PI1" t="inlineStr"/>
+      <c r="PJ1" t="inlineStr"/>
+      <c r="PK1" t="inlineStr"/>
+      <c r="PL1" t="inlineStr"/>
+      <c r="PM1" t="inlineStr"/>
+      <c r="PN1" t="inlineStr"/>
+      <c r="PO1" t="inlineStr"/>
+      <c r="PP1" t="inlineStr"/>
+      <c r="PQ1" t="inlineStr"/>
+      <c r="PR1" t="inlineStr"/>
+      <c r="PS1" t="inlineStr"/>
+      <c r="PT1" t="inlineStr"/>
+      <c r="PU1" t="inlineStr"/>
+      <c r="PV1" t="inlineStr"/>
+      <c r="PW1" t="inlineStr"/>
+      <c r="PX1" t="inlineStr"/>
+      <c r="PY1" t="inlineStr"/>
+      <c r="PZ1" t="inlineStr"/>
+      <c r="QA1" t="inlineStr"/>
+      <c r="QB1" t="inlineStr"/>
+      <c r="QC1" t="inlineStr"/>
+      <c r="QD1" t="inlineStr"/>
+      <c r="QE1" t="inlineStr"/>
+      <c r="QF1" t="inlineStr"/>
+      <c r="QG1" t="inlineStr"/>
+      <c r="QH1" t="inlineStr"/>
+      <c r="QI1" t="inlineStr"/>
+      <c r="QJ1" t="inlineStr"/>
+      <c r="QK1" t="inlineStr"/>
+      <c r="QL1" t="inlineStr"/>
+      <c r="QM1" t="inlineStr"/>
+      <c r="QN1" t="inlineStr"/>
+      <c r="QO1" t="inlineStr"/>
+      <c r="QP1" t="inlineStr"/>
+      <c r="QQ1" t="inlineStr"/>
+      <c r="QR1" t="inlineStr"/>
+      <c r="QS1" t="inlineStr"/>
+      <c r="QT1" t="inlineStr"/>
+      <c r="QU1" t="inlineStr"/>
+      <c r="QV1" t="inlineStr"/>
+      <c r="QW1" t="inlineStr"/>
+      <c r="QX1" t="inlineStr"/>
+      <c r="QY1" t="inlineStr"/>
+      <c r="QZ1" t="inlineStr"/>
+      <c r="RA1" t="inlineStr"/>
+      <c r="RB1" t="inlineStr"/>
+      <c r="RC1" t="inlineStr"/>
+      <c r="RD1" t="inlineStr"/>
+      <c r="RE1" t="inlineStr"/>
+      <c r="RF1" t="inlineStr"/>
+      <c r="RG1" t="inlineStr"/>
+      <c r="RH1" t="inlineStr"/>
+      <c r="RI1" t="inlineStr"/>
+      <c r="RJ1" t="inlineStr"/>
+      <c r="RK1" t="inlineStr"/>
+      <c r="RL1" t="inlineStr"/>
+      <c r="RM1" t="inlineStr"/>
+      <c r="RN1" t="inlineStr"/>
+      <c r="RO1" t="inlineStr"/>
+      <c r="RP1" t="inlineStr"/>
+      <c r="RQ1" t="inlineStr"/>
+      <c r="RR1" t="inlineStr"/>
+      <c r="RS1" t="inlineStr"/>
+      <c r="RT1" t="inlineStr"/>
+      <c r="RU1" t="inlineStr"/>
+      <c r="RV1" t="inlineStr"/>
+      <c r="RW1" t="inlineStr"/>
+      <c r="RX1" t="inlineStr"/>
+      <c r="RY1" t="inlineStr"/>
+      <c r="RZ1" t="inlineStr"/>
+      <c r="SA1" t="inlineStr"/>
+      <c r="SB1" t="inlineStr"/>
+      <c r="SC1" t="inlineStr"/>
+      <c r="SD1" t="inlineStr"/>
+      <c r="SE1" t="inlineStr"/>
+      <c r="SF1" t="inlineStr"/>
+      <c r="SG1" t="inlineStr"/>
+      <c r="SH1" t="inlineStr"/>
+      <c r="SI1" t="inlineStr"/>
+      <c r="SJ1" t="inlineStr"/>
+      <c r="SK1" t="inlineStr"/>
+      <c r="SL1" t="inlineStr"/>
+      <c r="SM1" t="inlineStr"/>
+      <c r="SN1" t="inlineStr"/>
+      <c r="SO1" t="inlineStr"/>
+      <c r="SP1" t="inlineStr"/>
+      <c r="SQ1" t="inlineStr"/>
+      <c r="SR1" t="inlineStr"/>
+      <c r="SS1" t="inlineStr"/>
+      <c r="ST1" t="inlineStr"/>
+      <c r="SU1" t="inlineStr"/>
+      <c r="SV1" t="inlineStr"/>
+      <c r="SW1" t="inlineStr"/>
+      <c r="SX1" t="inlineStr"/>
+      <c r="SY1" t="inlineStr"/>
+      <c r="SZ1" t="inlineStr"/>
+      <c r="TA1" t="inlineStr"/>
+      <c r="TB1" t="inlineStr"/>
+      <c r="TC1" t="inlineStr"/>
+      <c r="TD1" t="inlineStr"/>
+      <c r="TE1" t="inlineStr"/>
+      <c r="TF1" t="inlineStr"/>
+      <c r="TG1" t="inlineStr"/>
+      <c r="TH1" t="inlineStr"/>
+      <c r="TI1" t="inlineStr"/>
+      <c r="TJ1" t="inlineStr"/>
+      <c r="TK1" t="inlineStr"/>
+      <c r="TL1" t="inlineStr"/>
+      <c r="TM1" t="inlineStr"/>
+      <c r="TN1" t="inlineStr"/>
+      <c r="TO1" t="inlineStr"/>
+      <c r="TP1" t="inlineStr"/>
+      <c r="TQ1" t="inlineStr"/>
+      <c r="TR1" t="inlineStr"/>
+      <c r="TS1" t="inlineStr"/>
+      <c r="TT1" t="inlineStr"/>
+      <c r="TU1" t="inlineStr"/>
+      <c r="TV1" t="inlineStr"/>
+      <c r="TW1" t="inlineStr"/>
+      <c r="TX1" t="inlineStr"/>
+      <c r="TY1" t="inlineStr"/>
+      <c r="TZ1" t="inlineStr"/>
+      <c r="UA1" t="inlineStr"/>
+      <c r="UB1" t="inlineStr"/>
+      <c r="UC1" t="inlineStr"/>
+      <c r="UD1" t="inlineStr"/>
+      <c r="UE1" t="inlineStr"/>
+      <c r="UF1" t="inlineStr"/>
+      <c r="UG1" t="inlineStr"/>
+      <c r="UH1" t="inlineStr"/>
+      <c r="UI1" t="inlineStr"/>
+      <c r="UJ1" t="inlineStr"/>
+      <c r="UK1" t="inlineStr"/>
+      <c r="UL1" t="inlineStr"/>
+      <c r="UM1" t="inlineStr"/>
+      <c r="UN1" t="inlineStr"/>
+      <c r="UO1" t="inlineStr"/>
+      <c r="UP1" t="inlineStr"/>
+      <c r="UQ1" t="inlineStr"/>
+      <c r="UR1" t="inlineStr"/>
+      <c r="US1" t="inlineStr"/>
+      <c r="UT1" t="inlineStr"/>
+      <c r="UU1" t="inlineStr"/>
+      <c r="UV1" t="inlineStr"/>
+      <c r="UW1" t="inlineStr"/>
+      <c r="UX1" t="inlineStr"/>
+      <c r="UY1" t="inlineStr"/>
+      <c r="UZ1" t="inlineStr"/>
+      <c r="VA1" t="inlineStr"/>
+      <c r="VB1" t="inlineStr"/>
+      <c r="VC1" t="inlineStr"/>
+      <c r="VD1" t="inlineStr"/>
+      <c r="VE1" t="inlineStr"/>
+      <c r="VF1" t="inlineStr"/>
+      <c r="VG1" t="inlineStr"/>
+      <c r="VH1" t="inlineStr"/>
+      <c r="VI1" t="inlineStr"/>
+      <c r="VJ1" t="inlineStr"/>
+      <c r="VK1" t="inlineStr"/>
+      <c r="VL1" t="inlineStr"/>
+      <c r="VM1" t="inlineStr"/>
+      <c r="VN1" t="inlineStr"/>
+      <c r="VO1" t="inlineStr"/>
+      <c r="VP1" t="inlineStr"/>
+      <c r="VQ1" t="inlineStr"/>
+      <c r="VR1" t="inlineStr"/>
+      <c r="VS1" t="inlineStr"/>
+      <c r="VT1" t="inlineStr"/>
+      <c r="VU1" t="inlineStr"/>
+      <c r="VV1" t="inlineStr"/>
+      <c r="VW1" t="inlineStr"/>
+      <c r="VX1" t="inlineStr"/>
+      <c r="VY1" t="inlineStr"/>
+      <c r="VZ1" t="inlineStr"/>
+      <c r="WA1" t="inlineStr"/>
+      <c r="WB1" t="inlineStr"/>
+      <c r="WC1" t="inlineStr"/>
+      <c r="WD1" t="inlineStr"/>
+      <c r="WE1" t="inlineStr"/>
+      <c r="WF1" t="inlineStr"/>
+      <c r="WG1" t="inlineStr"/>
+      <c r="WH1" t="inlineStr"/>
+      <c r="WI1" t="inlineStr"/>
+      <c r="WJ1" t="inlineStr"/>
+      <c r="WK1" t="inlineStr"/>
+      <c r="WL1" t="inlineStr"/>
+      <c r="WM1" t="inlineStr"/>
+      <c r="WN1" t="inlineStr"/>
+      <c r="WO1" t="inlineStr"/>
+      <c r="WP1" t="inlineStr"/>
+      <c r="WQ1" t="inlineStr"/>
+      <c r="WR1" t="inlineStr"/>
+      <c r="WS1" t="inlineStr"/>
+      <c r="WT1" t="inlineStr"/>
+      <c r="WU1" t="inlineStr"/>
+      <c r="WV1" t="inlineStr"/>
+      <c r="WW1" t="inlineStr"/>
+      <c r="WX1" t="inlineStr"/>
+      <c r="WY1" t="inlineStr"/>
+      <c r="WZ1" t="inlineStr"/>
+      <c r="XA1" t="inlineStr"/>
+      <c r="XB1" t="inlineStr"/>
+      <c r="XC1" t="inlineStr"/>
+      <c r="XD1" t="inlineStr"/>
+      <c r="XE1" t="inlineStr"/>
+      <c r="XF1" t="inlineStr"/>
+      <c r="XG1" t="inlineStr"/>
+      <c r="XH1" t="inlineStr"/>
+      <c r="XI1" t="inlineStr"/>
+      <c r="XJ1" t="inlineStr"/>
+      <c r="XK1" t="inlineStr"/>
+      <c r="XL1" t="inlineStr"/>
+      <c r="XM1" t="inlineStr"/>
+      <c r="XN1" t="inlineStr"/>
+      <c r="XO1" t="inlineStr"/>
+      <c r="XP1" t="inlineStr"/>
+      <c r="XQ1" t="inlineStr"/>
+      <c r="XR1" t="inlineStr"/>
+      <c r="XS1" t="inlineStr"/>
+      <c r="XT1" t="inlineStr"/>
+      <c r="XU1" t="inlineStr"/>
+      <c r="XV1" t="inlineStr"/>
+      <c r="XW1" t="inlineStr"/>
+      <c r="XX1" t="inlineStr"/>
+      <c r="XY1" t="inlineStr"/>
+      <c r="XZ1" t="inlineStr"/>
+      <c r="YA1" t="inlineStr"/>
+      <c r="YB1" t="inlineStr"/>
+      <c r="YC1" t="inlineStr"/>
+      <c r="YD1" t="inlineStr"/>
+      <c r="YE1" t="inlineStr"/>
+      <c r="YF1" t="inlineStr"/>
+      <c r="YG1" t="inlineStr"/>
+      <c r="YH1" t="inlineStr"/>
+      <c r="YI1" t="inlineStr"/>
+      <c r="YJ1" t="inlineStr"/>
+      <c r="YK1" t="inlineStr"/>
+      <c r="YL1" t="inlineStr"/>
+      <c r="YM1" t="inlineStr"/>
+      <c r="YN1" t="inlineStr"/>
+      <c r="YO1" t="inlineStr"/>
+      <c r="YP1" t="inlineStr"/>
+      <c r="YQ1" t="inlineStr"/>
+      <c r="YR1" t="inlineStr"/>
+      <c r="YS1" t="inlineStr"/>
+      <c r="YT1" t="inlineStr"/>
+      <c r="YU1" t="inlineStr"/>
+      <c r="YV1" t="inlineStr"/>
+      <c r="YW1" t="inlineStr"/>
+      <c r="YX1" t="inlineStr"/>
+      <c r="YY1" t="inlineStr"/>
+      <c r="YZ1" t="inlineStr"/>
+      <c r="ZA1" t="inlineStr"/>
+      <c r="ZB1" t="inlineStr"/>
+      <c r="ZC1" t="inlineStr"/>
+      <c r="ZD1" t="inlineStr"/>
+      <c r="ZE1" t="inlineStr"/>
+      <c r="ZF1" t="inlineStr"/>
+      <c r="ZG1" t="inlineStr"/>
+      <c r="ZH1" t="inlineStr"/>
+      <c r="ZI1" t="inlineStr"/>
+      <c r="ZJ1" t="inlineStr"/>
+      <c r="ZK1" t="inlineStr"/>
+      <c r="ZL1" t="inlineStr"/>
+      <c r="ZM1" t="inlineStr"/>
+      <c r="ZN1" t="inlineStr"/>
+      <c r="ZO1" t="inlineStr"/>
+      <c r="ZP1" t="inlineStr"/>
+      <c r="ZQ1" t="inlineStr"/>
+      <c r="ZR1" t="inlineStr"/>
+      <c r="ZS1" t="inlineStr"/>
+      <c r="ZT1" t="inlineStr"/>
+      <c r="ZU1" t="inlineStr"/>
+      <c r="ZV1" t="inlineStr"/>
+      <c r="ZW1" t="inlineStr"/>
+      <c r="ZX1" t="inlineStr"/>
+      <c r="ZY1" t="inlineStr"/>
+      <c r="ZZ1" t="inlineStr"/>
+      <c r="AAA1" t="inlineStr"/>
+      <c r="AAB1" t="inlineStr"/>
+      <c r="AAC1" t="inlineStr"/>
+      <c r="AAD1" t="inlineStr"/>
+      <c r="AAE1" t="inlineStr"/>
+      <c r="AAF1" t="inlineStr"/>
+      <c r="AAG1" t="inlineStr"/>
+      <c r="AAH1" t="inlineStr"/>
+      <c r="AAI1" t="inlineStr"/>
+      <c r="AAJ1" t="inlineStr"/>
+      <c r="AAK1" t="inlineStr"/>
+      <c r="AAL1" t="inlineStr"/>
+      <c r="AAM1" t="inlineStr"/>
+      <c r="AAN1" t="inlineStr"/>
+      <c r="AAO1" t="inlineStr"/>
+      <c r="AAP1" t="inlineStr"/>
+      <c r="AAQ1" t="inlineStr"/>
+      <c r="AAR1" t="inlineStr"/>
+      <c r="AAS1" t="inlineStr"/>
+      <c r="AAT1" t="inlineStr"/>
+      <c r="AAU1" t="inlineStr"/>
+      <c r="AAV1" t="inlineStr"/>
+      <c r="AAW1" t="inlineStr"/>
+      <c r="AAX1" t="inlineStr"/>
+      <c r="AAY1" t="inlineStr"/>
+      <c r="AAZ1" t="inlineStr"/>
+      <c r="ABA1" t="inlineStr"/>
+      <c r="ABB1" t="inlineStr"/>
+      <c r="ABC1" t="inlineStr"/>
+      <c r="ABD1" t="inlineStr"/>
+      <c r="ABE1" t="inlineStr"/>
+      <c r="ABF1" t="inlineStr"/>
+      <c r="ABG1" t="inlineStr"/>
+      <c r="ABH1" t="inlineStr"/>
+      <c r="ABI1" t="inlineStr"/>
+      <c r="ABJ1" t="inlineStr"/>
+      <c r="ABK1" t="inlineStr"/>
+      <c r="ABL1" t="inlineStr"/>
+      <c r="ABM1" t="inlineStr"/>
+      <c r="ABN1" t="inlineStr"/>
+      <c r="ABO1" t="inlineStr"/>
+      <c r="ABP1" t="inlineStr"/>
+      <c r="ABQ1" t="inlineStr"/>
+      <c r="ABR1" t="inlineStr"/>
+      <c r="ABS1" t="inlineStr"/>
+      <c r="ABT1" t="inlineStr"/>
+      <c r="ABU1" t="inlineStr"/>
+      <c r="ABV1" t="inlineStr"/>
+      <c r="ABW1" t="inlineStr"/>
+      <c r="ABX1" t="inlineStr"/>
+      <c r="ABY1" t="inlineStr"/>
+      <c r="ABZ1" t="inlineStr"/>
+      <c r="ACA1" t="inlineStr"/>
+      <c r="ACB1" t="inlineStr"/>
+      <c r="ACC1" t="inlineStr"/>
+      <c r="ACD1" t="inlineStr"/>
+      <c r="ACE1" t="inlineStr"/>
+      <c r="ACF1" t="inlineStr"/>
+      <c r="ACG1" t="inlineStr"/>
+      <c r="ACH1" t="inlineStr"/>
+      <c r="ACI1" t="inlineStr"/>
+      <c r="ACJ1" t="inlineStr"/>
+      <c r="ACK1" t="inlineStr"/>
+      <c r="ACL1" t="inlineStr"/>
+      <c r="ACM1" t="inlineStr"/>
+      <c r="ACN1" t="inlineStr"/>
+      <c r="ACO1" t="inlineStr"/>
+      <c r="ACP1" t="inlineStr"/>
+      <c r="ACQ1" t="inlineStr"/>
+      <c r="ACR1" t="inlineStr"/>
+      <c r="ACS1" t="inlineStr"/>
+      <c r="ACT1" t="inlineStr"/>
+      <c r="ACU1" t="inlineStr"/>
+      <c r="ACV1" t="inlineStr"/>
+      <c r="ACW1" t="inlineStr"/>
+      <c r="ACX1" t="inlineStr"/>
+      <c r="ACY1" t="inlineStr"/>
+      <c r="ACZ1" t="inlineStr"/>
+      <c r="ADA1" t="inlineStr"/>
+      <c r="ADB1" t="inlineStr"/>
+      <c r="ADC1" t="inlineStr"/>
+      <c r="ADD1" t="inlineStr"/>
+      <c r="ADE1" t="inlineStr"/>
+      <c r="ADF1" t="inlineStr"/>
+      <c r="ADG1" t="inlineStr"/>
+      <c r="ADH1" t="inlineStr"/>
+      <c r="ADI1" t="inlineStr"/>
+      <c r="ADJ1" t="inlineStr"/>
+      <c r="ADK1" t="inlineStr"/>
+      <c r="ADL1" t="inlineStr"/>
+      <c r="ADM1" t="inlineStr"/>
+      <c r="ADN1" t="inlineStr"/>
+      <c r="ADO1" t="inlineStr"/>
+      <c r="ADP1" t="inlineStr"/>
+      <c r="ADQ1" t="inlineStr"/>
+      <c r="ADR1" t="inlineStr"/>
+      <c r="ADS1" t="inlineStr"/>
+      <c r="ADT1" t="inlineStr"/>
+      <c r="ADU1" t="inlineStr"/>
+      <c r="ADV1" t="inlineStr"/>
+      <c r="ADW1" t="inlineStr"/>
+      <c r="ADX1" t="inlineStr"/>
+      <c r="ADY1" t="inlineStr"/>
+      <c r="ADZ1" t="inlineStr"/>
+      <c r="AEA1" t="inlineStr"/>
+      <c r="AEB1" t="inlineStr"/>
+      <c r="AEC1" t="inlineStr"/>
+      <c r="AED1" t="inlineStr"/>
+      <c r="AEE1" t="inlineStr"/>
+      <c r="AEF1" t="inlineStr"/>
+      <c r="AEG1" t="inlineStr"/>
+      <c r="AEH1" t="inlineStr"/>
+      <c r="AEI1" t="inlineStr"/>
+      <c r="AEJ1" t="inlineStr"/>
+      <c r="AEK1" t="inlineStr"/>
+      <c r="AEL1" t="inlineStr"/>
+      <c r="AEM1" t="inlineStr"/>
+      <c r="AEN1" t="inlineStr"/>
+      <c r="AEO1" t="inlineStr"/>
+      <c r="AEP1" t="inlineStr"/>
+      <c r="AEQ1" t="inlineStr"/>
+      <c r="AER1" t="inlineStr"/>
+      <c r="AES1" t="inlineStr"/>
+      <c r="AET1" t="inlineStr"/>
+      <c r="AEU1" t="inlineStr"/>
+      <c r="AEV1" t="inlineStr"/>
+      <c r="AEW1" t="inlineStr"/>
+      <c r="AEX1" t="inlineStr"/>
+      <c r="AEY1" t="inlineStr"/>
+      <c r="AEZ1" t="inlineStr"/>
+      <c r="AFA1" t="inlineStr"/>
+      <c r="AFB1" t="inlineStr"/>
+      <c r="AFC1" t="inlineStr"/>
+      <c r="AFD1" t="inlineStr"/>
+      <c r="AFE1" t="inlineStr"/>
+      <c r="AFF1" t="inlineStr"/>
+      <c r="AFG1" t="inlineStr"/>
+      <c r="AFH1" t="inlineStr"/>
+      <c r="AFI1" t="inlineStr"/>
+      <c r="AFJ1" t="inlineStr"/>
+      <c r="AFK1" t="inlineStr"/>
+      <c r="AFL1" t="inlineStr"/>
+      <c r="AFM1" t="inlineStr"/>
+      <c r="AFN1" t="inlineStr"/>
+      <c r="AFO1" t="inlineStr"/>
+      <c r="AFP1" t="inlineStr"/>
+      <c r="AFQ1" t="inlineStr"/>
+      <c r="AFR1" t="inlineStr"/>
+      <c r="AFS1" t="inlineStr"/>
+      <c r="AFT1" t="inlineStr"/>
+      <c r="AFU1" t="inlineStr"/>
+      <c r="AFV1" t="inlineStr"/>
+      <c r="AFW1" t="inlineStr"/>
+      <c r="AFX1" t="inlineStr"/>
+      <c r="AFY1" t="inlineStr"/>
+      <c r="AFZ1" t="inlineStr"/>
+      <c r="AGA1" t="inlineStr"/>
+      <c r="AGB1" t="inlineStr"/>
+      <c r="AGC1" t="inlineStr"/>
+      <c r="AGD1" t="inlineStr"/>
+      <c r="AGE1" t="inlineStr"/>
+      <c r="AGF1" t="inlineStr"/>
+      <c r="AGG1" t="inlineStr"/>
+      <c r="AGH1" t="inlineStr"/>
+      <c r="AGI1" t="inlineStr"/>
+      <c r="AGJ1" t="inlineStr"/>
+      <c r="AGK1" t="inlineStr"/>
+      <c r="AGL1" t="inlineStr"/>
+      <c r="AGM1" t="inlineStr"/>
+      <c r="AGN1" t="inlineStr"/>
+      <c r="AGO1" t="inlineStr"/>
+      <c r="AGP1" t="inlineStr"/>
+      <c r="AGQ1" t="inlineStr"/>
+      <c r="AGR1" t="inlineStr"/>
+      <c r="AGS1" t="inlineStr"/>
+      <c r="AGT1" t="inlineStr"/>
+      <c r="AGU1" t="inlineStr"/>
+      <c r="AGV1" t="inlineStr"/>
+      <c r="AGW1" t="inlineStr"/>
+      <c r="AGX1" t="inlineStr"/>
+      <c r="AGY1" t="inlineStr"/>
+      <c r="AGZ1" t="inlineStr"/>
+      <c r="AHA1" t="inlineStr"/>
+      <c r="AHB1" t="inlineStr"/>
+      <c r="AHC1" t="inlineStr"/>
+      <c r="AHD1" t="inlineStr"/>
+      <c r="AHE1" t="inlineStr"/>
+      <c r="AHF1" t="inlineStr"/>
+      <c r="AHG1" t="inlineStr"/>
+      <c r="AHH1" t="inlineStr"/>
+      <c r="AHI1" t="inlineStr"/>
+      <c r="AHJ1" t="inlineStr"/>
+      <c r="AHK1" t="inlineStr"/>
+      <c r="AHL1" t="inlineStr"/>
+      <c r="AHM1" t="inlineStr"/>
+      <c r="AHN1" t="inlineStr"/>
+      <c r="AHO1" t="inlineStr"/>
+      <c r="AHP1" t="inlineStr"/>
+      <c r="AHQ1" t="inlineStr"/>
+      <c r="AHR1" t="inlineStr"/>
+      <c r="AHS1" t="inlineStr"/>
+      <c r="AHT1" t="inlineStr"/>
+      <c r="AHU1" t="inlineStr"/>
+      <c r="AHV1" t="inlineStr"/>
+      <c r="AHW1" t="inlineStr"/>
+      <c r="AHX1" t="inlineStr"/>
+      <c r="AHY1" t="inlineStr"/>
+      <c r="AHZ1" t="inlineStr"/>
+      <c r="AIA1" t="inlineStr"/>
+      <c r="AIB1" t="inlineStr"/>
+      <c r="AIC1" t="inlineStr"/>
+      <c r="AID1" t="inlineStr"/>
+      <c r="AIE1" t="inlineStr"/>
+      <c r="AIF1" t="inlineStr"/>
+      <c r="AIG1" t="inlineStr"/>
+      <c r="AIH1" t="inlineStr"/>
+      <c r="AII1" t="inlineStr"/>
+      <c r="AIJ1" t="inlineStr"/>
+      <c r="AIK1" t="inlineStr"/>
+      <c r="AIL1" t="inlineStr"/>
+      <c r="AIM1" t="inlineStr"/>
+      <c r="AIN1" t="inlineStr"/>
+      <c r="AIO1" t="inlineStr"/>
+      <c r="AIP1" t="inlineStr"/>
+      <c r="AIQ1" t="inlineStr"/>
+      <c r="AIR1" t="inlineStr"/>
+      <c r="AIS1" t="inlineStr"/>
+      <c r="AIT1" t="inlineStr"/>
+      <c r="AIU1" t="inlineStr"/>
+      <c r="AIV1" t="inlineStr"/>
+      <c r="AIW1" t="inlineStr"/>
+      <c r="AIX1" t="inlineStr"/>
+      <c r="AIY1" t="inlineStr"/>
+      <c r="AIZ1" t="inlineStr"/>
+      <c r="AJA1" t="inlineStr"/>
+      <c r="AJB1" t="inlineStr"/>
+      <c r="AJC1" t="inlineStr"/>
+      <c r="AJD1" t="inlineStr"/>
+      <c r="AJE1" t="inlineStr"/>
+      <c r="AJF1" t="inlineStr"/>
+      <c r="AJG1" t="inlineStr"/>
+      <c r="AJH1" t="inlineStr"/>
+      <c r="AJI1" t="inlineStr"/>
+      <c r="AJJ1" t="inlineStr"/>
+      <c r="AJK1" t="inlineStr"/>
+      <c r="AJL1" t="inlineStr"/>
+      <c r="AJM1" t="inlineStr"/>
+      <c r="AJN1" t="inlineStr"/>
+      <c r="AJO1" t="inlineStr"/>
+      <c r="AJP1" t="inlineStr"/>
+      <c r="AJQ1" t="inlineStr"/>
+      <c r="AJR1" t="inlineStr"/>
+      <c r="AJS1" t="inlineStr"/>
+      <c r="AJT1" t="inlineStr"/>
+      <c r="AJU1" t="inlineStr"/>
+      <c r="AJV1" t="inlineStr"/>
+      <c r="AJW1" t="inlineStr"/>
+      <c r="AJX1" t="inlineStr"/>
+      <c r="AJY1" t="inlineStr"/>
+      <c r="AJZ1" t="inlineStr"/>
+      <c r="AKA1" t="inlineStr"/>
+      <c r="AKB1" t="inlineStr"/>
+      <c r="AKC1" t="inlineStr"/>
+      <c r="AKD1" t="inlineStr"/>
+      <c r="AKE1" t="inlineStr"/>
+      <c r="AKF1" t="inlineStr"/>
+      <c r="AKG1" t="inlineStr"/>
+      <c r="AKH1" t="inlineStr"/>
+      <c r="AKI1" t="inlineStr"/>
+      <c r="AKJ1" t="inlineStr"/>
+      <c r="AKK1" t="inlineStr"/>
+      <c r="AKL1" t="inlineStr"/>
+      <c r="AKM1" t="inlineStr"/>
+      <c r="AKN1" t="inlineStr"/>
+      <c r="AKO1" t="inlineStr"/>
+      <c r="AKP1" t="inlineStr"/>
+      <c r="AKQ1" t="inlineStr"/>
+      <c r="AKR1" t="inlineStr"/>
+      <c r="AKS1" t="inlineStr"/>
+      <c r="AKT1" t="inlineStr"/>
+      <c r="AKU1" t="inlineStr"/>
+      <c r="AKV1" t="inlineStr"/>
+      <c r="AKW1" t="inlineStr"/>
+      <c r="AKX1" t="inlineStr"/>
+      <c r="AKY1" t="inlineStr"/>
+      <c r="AKZ1" t="inlineStr"/>
+      <c r="ALA1" t="inlineStr"/>
+      <c r="ALB1" t="inlineStr"/>
+      <c r="ALC1" t="inlineStr"/>
+      <c r="ALD1" t="inlineStr"/>
+      <c r="ALE1" t="inlineStr"/>
+      <c r="ALF1" t="inlineStr"/>
+      <c r="ALG1" t="inlineStr"/>
+      <c r="ALH1" t="inlineStr"/>
+      <c r="ALI1" t="inlineStr"/>
+      <c r="ALJ1" t="inlineStr"/>
+      <c r="ALK1" t="inlineStr"/>
+      <c r="ALL1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121752</v>
+        <v>894500</v>
       </c>
       <c r="B2" t="n">
-        <v>230611</v>
+        <v>356054</v>
       </c>
       <c r="C2" t="n">
-        <v>425940</v>
+        <v>37912</v>
       </c>
       <c r="D2" t="n">
-        <v>401557</v>
+        <v>591402</v>
       </c>
       <c r="E2" t="n">
-        <v>791054</v>
+        <v>699500</v>
       </c>
       <c r="F2" t="n">
-        <v>169900</v>
+        <v>816608</v>
       </c>
       <c r="G2" t="n">
-        <v>446281</v>
+        <v>1157324</v>
       </c>
       <c r="H2" t="n">
-        <v>182093</v>
+        <v>220868</v>
       </c>
       <c r="I2" t="n">
-        <v>807488</v>
+        <v>814810</v>
       </c>
       <c r="J2" t="n">
-        <v>263204</v>
+        <v>730337</v>
       </c>
       <c r="K2" t="n">
-        <v>466384</v>
+        <v>696353</v>
       </c>
       <c r="L2" t="n">
-        <v>177692</v>
+        <v>27403</v>
       </c>
       <c r="M2" t="n">
-        <v>3150</v>
+        <v>441712</v>
       </c>
       <c r="N2" t="n">
-        <v>147106</v>
+        <v>1171951</v>
       </c>
       <c r="O2" t="n">
-        <v>106106</v>
+        <v>468649</v>
       </c>
       <c r="P2" t="n">
-        <v>523286</v>
+        <v>780198</v>
       </c>
       <c r="Q2" t="n">
-        <v>696603</v>
+        <v>338238</v>
       </c>
       <c r="R2" t="n">
+        <v>89353</v>
+      </c>
+      <c r="S2" t="n">
+        <v>243786</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1148800</v>
+      </c>
+      <c r="U2" t="n">
+        <v>93364</v>
+      </c>
+      <c r="V2" t="n">
+        <v>724219</v>
+      </c>
+      <c r="W2" t="n">
+        <v>703068</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1026640</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>602676</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>675397</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>589922</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>646464</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>115703</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>925118</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>789605</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1223018</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>354217</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>835637</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>300258</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1069575</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>657301</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1021610</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>740519</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>967968</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1031586</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>682864</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>201090</v>
+      </c>
+      <c r="AR2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="n">
-        <v>66513</v>
-      </c>
-      <c r="T2" t="n">
-        <v>493736</v>
-      </c>
-      <c r="U2" t="n">
-        <v>498060</v>
-      </c>
-      <c r="V2" t="n">
-        <v>702683</v>
-      </c>
-      <c r="W2" t="n">
-        <v>318992</v>
-      </c>
-      <c r="X2" t="n">
-        <v>473990</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>438896</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1217</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>827422</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>216963</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>604148</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>628088</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>590478</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>264531</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3191</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>651689</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>123821</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>756415</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>151078</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>134571</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>419978</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>65889</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>245814</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>561450</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>211130</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>265779</v>
-      </c>
       <c r="AS2" t="n">
-        <v>674552</v>
+        <v>850496</v>
       </c>
       <c r="AT2" t="n">
-        <v>657702</v>
+        <v>648926</v>
       </c>
       <c r="AU2" t="n">
-        <v>548595</v>
+        <v>1022613</v>
       </c>
       <c r="AV2" t="n">
-        <v>746488</v>
+        <v>71260</v>
       </c>
       <c r="AW2" t="n">
-        <v>634557</v>
+        <v>157184</v>
       </c>
       <c r="AX2" t="n">
-        <v>167352</v>
+        <v>150219</v>
       </c>
       <c r="AY2" t="n">
-        <v>612978</v>
+        <v>490456</v>
       </c>
       <c r="AZ2" t="n">
-        <v>408576</v>
+        <v>830633</v>
       </c>
       <c r="BA2" t="n">
-        <v>535285</v>
+        <v>1087818</v>
       </c>
       <c r="BB2" t="n">
-        <v>376851</v>
+        <v>434101</v>
       </c>
       <c r="BC2" t="n">
-        <v>207166</v>
+        <v>525248</v>
       </c>
       <c r="BD2" t="n">
-        <v>213445</v>
+        <v>15634</v>
       </c>
       <c r="BE2" t="n">
-        <v>265494</v>
+        <v>298343</v>
       </c>
       <c r="BF2" t="n">
-        <v>347976</v>
+        <v>1111337</v>
       </c>
       <c r="BG2" t="n">
-        <v>270864</v>
+        <v>188559</v>
       </c>
       <c r="BH2" t="n">
-        <v>511238</v>
+        <v>287237</v>
       </c>
       <c r="BI2" t="n">
-        <v>701989</v>
+        <v>720039</v>
       </c>
       <c r="BJ2" t="n">
-        <v>493538</v>
+        <v>256352</v>
       </c>
       <c r="BK2" t="n">
-        <v>826157</v>
+        <v>209994</v>
       </c>
       <c r="BL2" t="n">
-        <v>293638</v>
+        <v>190677</v>
       </c>
       <c r="BM2" t="n">
-        <v>687641</v>
+        <v>504950</v>
       </c>
       <c r="BN2" t="n">
-        <v>322686</v>
+        <v>289599</v>
       </c>
       <c r="BO2" t="n">
-        <v>565668</v>
+        <v>325534</v>
       </c>
       <c r="BP2" t="n">
-        <v>608896</v>
+        <v>234108</v>
       </c>
       <c r="BQ2" t="n">
-        <v>433421</v>
+        <v>358138</v>
       </c>
       <c r="BR2" t="n">
-        <v>35991</v>
+        <v>621660</v>
       </c>
       <c r="BS2" t="n">
-        <v>72557</v>
+        <v>651079</v>
       </c>
       <c r="BT2" t="n">
-        <v>145479</v>
+        <v>1013750</v>
       </c>
       <c r="BU2" t="n">
-        <v>834416</v>
+        <v>786219</v>
       </c>
       <c r="BV2" t="n">
-        <v>359291</v>
+        <v>131458</v>
       </c>
       <c r="BW2" t="n">
-        <v>685487</v>
+        <v>226935</v>
       </c>
       <c r="BX2" t="n">
-        <v>51884</v>
+        <v>605688</v>
       </c>
       <c r="BY2" t="n">
-        <v>324818</v>
+        <v>454413</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1799</v>
+        <v>1191620</v>
       </c>
       <c r="CA2" t="n">
-        <v>478737</v>
+        <v>113754</v>
       </c>
       <c r="CB2" t="n">
-        <v>299733</v>
+        <v>605581</v>
       </c>
       <c r="CC2" t="n">
-        <v>534559</v>
+        <v>453097</v>
       </c>
       <c r="CD2" t="n">
-        <v>756327</v>
+        <v>248560</v>
       </c>
       <c r="CE2" t="n">
-        <v>578596</v>
+        <v>61014</v>
       </c>
       <c r="CF2" t="n">
-        <v>787333</v>
+        <v>914906</v>
       </c>
       <c r="CG2" t="n">
-        <v>194548</v>
+        <v>335335</v>
       </c>
       <c r="CH2" t="n">
-        <v>454946</v>
+        <v>773631</v>
       </c>
       <c r="CI2" t="n">
-        <v>324392</v>
+        <v>53379</v>
       </c>
       <c r="CJ2" t="n">
-        <v>104268</v>
+        <v>317359</v>
       </c>
       <c r="CK2" t="n">
-        <v>575831</v>
+        <v>822727</v>
       </c>
       <c r="CL2" t="n">
-        <v>4199</v>
+        <v>555302</v>
       </c>
       <c r="CM2" t="n">
-        <v>373627</v>
+        <v>1082884</v>
       </c>
       <c r="CN2" t="n">
-        <v>24396</v>
+        <v>724748</v>
       </c>
       <c r="CO2" t="n">
-        <v>89903</v>
+        <v>617478</v>
       </c>
       <c r="CP2" t="n">
-        <v>768552</v>
+        <v>937449</v>
       </c>
       <c r="CQ2" t="n">
-        <v>386229</v>
+        <v>96091</v>
       </c>
       <c r="CR2" t="n">
-        <v>574356</v>
+        <v>904094</v>
       </c>
       <c r="CS2" t="n">
-        <v>115163</v>
+        <v>400436</v>
       </c>
       <c r="CT2" t="n">
-        <v>483919</v>
+        <v>659503</v>
       </c>
       <c r="CU2" t="n">
-        <v>633350</v>
+        <v>159105</v>
       </c>
       <c r="CV2" t="n">
-        <v>739421</v>
+        <v>322838</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>335987</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>1076300</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>158253</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>536082</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>838100</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>128076</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>519278</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>111794</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>28064</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>49015</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1084682</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>855376</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>314478</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>352273</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>1168122</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>859542</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>1198092</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>383091</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>769654</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>129727</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>989657</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>975783</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>799750</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>242598</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1042208</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>960971</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1098285</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>944608</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>567943</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>773102</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>1203983</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>758117</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>457412</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>906496</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>720285</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>1146697</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>1156634</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>202757</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>425000</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>14005</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>252666</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>415760</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>929708</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>808832</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>679310</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>134946</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>25269</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>690074</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>217288</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>73592</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>199323</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>367779</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>566482</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>1179509</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>812521</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>451707</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>639874</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>996152</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>683743</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>185274</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>654510</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>6449</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>1131576</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>570756</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>907905</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>144567</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>363712</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>315822</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>65014</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>83305</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>1182203</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>414558</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>213921</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>1093827</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>176394</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>892875</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>766430</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>393770</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>964992</v>
+      </c>
+      <c r="FX2" t="n">
+        <v>42382</v>
+      </c>
+      <c r="FY2" t="n">
+        <v>579207</v>
+      </c>
+      <c r="FZ2" t="n">
+        <v>470285</v>
+      </c>
+      <c r="GA2" t="n">
+        <v>308004</v>
+      </c>
+      <c r="GB2" t="n">
+        <v>100151</v>
+      </c>
+      <c r="GC2" t="n">
+        <v>983284</v>
+      </c>
+      <c r="GD2" t="n">
+        <v>759991</v>
+      </c>
+      <c r="GE2" t="n">
+        <v>1164144</v>
+      </c>
+      <c r="GF2" t="n">
+        <v>554139</v>
+      </c>
+      <c r="GG2" t="n">
+        <v>689186</v>
+      </c>
+      <c r="GH2" t="n">
+        <v>816976</v>
+      </c>
+      <c r="GI2" t="n">
+        <v>732723</v>
+      </c>
+      <c r="GJ2" t="n">
+        <v>88812</v>
+      </c>
+      <c r="GK2" t="n">
+        <v>1154111</v>
+      </c>
+      <c r="GL2" t="n">
+        <v>1099450</v>
+      </c>
+      <c r="GM2" t="n">
+        <v>1225636</v>
+      </c>
+      <c r="GN2" t="n">
+        <v>1058429</v>
+      </c>
+      <c r="GO2" t="n">
+        <v>180065</v>
+      </c>
+      <c r="GP2" t="n">
+        <v>253857</v>
+      </c>
+      <c r="GQ2" t="n">
+        <v>263081</v>
+      </c>
+      <c r="GR2" t="n">
+        <v>77067</v>
+      </c>
+      <c r="GS2" t="n">
+        <v>898142</v>
+      </c>
+      <c r="GT2" t="n">
+        <v>487509</v>
+      </c>
+      <c r="GU2" t="n">
+        <v>156029</v>
+      </c>
+      <c r="GV2" t="n">
+        <v>176082</v>
+      </c>
+      <c r="GW2" t="n">
+        <v>197317</v>
+      </c>
+      <c r="GX2" t="n">
+        <v>910125</v>
+      </c>
+      <c r="GY2" t="n">
+        <v>578836</v>
+      </c>
+      <c r="GZ2" t="n">
+        <v>77497</v>
+      </c>
+      <c r="HA2" t="n">
+        <v>1110243</v>
+      </c>
+      <c r="HB2" t="n">
+        <v>364521</v>
+      </c>
+      <c r="HC2" t="n">
+        <v>596517</v>
+      </c>
+      <c r="HD2" t="n">
+        <v>830073</v>
+      </c>
+      <c r="HE2" t="n">
+        <v>776419</v>
+      </c>
+      <c r="HF2" t="n">
+        <v>201155</v>
+      </c>
+      <c r="HG2" t="n">
+        <v>770072</v>
+      </c>
+      <c r="HH2" t="n">
+        <v>1112517</v>
+      </c>
+      <c r="HI2" t="n">
+        <v>686908</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>16577</v>
+      </c>
+      <c r="HK2" t="n">
+        <v>1123108</v>
+      </c>
+      <c r="HL2" t="n">
+        <v>495059</v>
+      </c>
+      <c r="HM2" t="n">
+        <v>1046683</v>
+      </c>
+      <c r="HN2" t="n">
+        <v>192678</v>
+      </c>
+      <c r="HO2" t="n">
+        <v>792254</v>
+      </c>
+      <c r="HP2" t="n">
+        <v>235953</v>
+      </c>
+      <c r="HQ2" t="n">
+        <v>778806</v>
+      </c>
+      <c r="HR2" t="n">
+        <v>763931</v>
+      </c>
+      <c r="HS2" t="n">
+        <v>55227</v>
+      </c>
+      <c r="HT2" t="n">
+        <v>547847</v>
+      </c>
+      <c r="HU2" t="n">
+        <v>400014</v>
+      </c>
+      <c r="HV2" t="n">
+        <v>810802</v>
+      </c>
+      <c r="HW2" t="n">
+        <v>172197</v>
+      </c>
+      <c r="HX2" t="n">
+        <v>1196740</v>
+      </c>
+      <c r="HY2" t="n">
+        <v>302777</v>
+      </c>
+      <c r="HZ2" t="n">
+        <v>198224</v>
+      </c>
+      <c r="IA2" t="n">
+        <v>677074</v>
+      </c>
+      <c r="IB2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="IC2" t="n">
+        <v>346622</v>
+      </c>
+      <c r="ID2" t="n">
+        <v>503688</v>
+      </c>
+      <c r="IE2" t="n">
+        <v>1180545</v>
+      </c>
+      <c r="IF2" t="n">
+        <v>284288</v>
+      </c>
+      <c r="IG2" t="n">
+        <v>676754</v>
+      </c>
+      <c r="IH2" t="n">
+        <v>1193611</v>
+      </c>
+      <c r="II2" t="n">
+        <v>36782</v>
+      </c>
+      <c r="IJ2" t="n">
+        <v>5418</v>
+      </c>
+      <c r="IK2" t="n">
+        <v>959800</v>
+      </c>
+      <c r="IL2" t="n">
+        <v>1185457</v>
+      </c>
+      <c r="IM2" t="n">
+        <v>229124</v>
+      </c>
+      <c r="IN2" t="n">
+        <v>623700</v>
+      </c>
+      <c r="IO2" t="n">
+        <v>906150</v>
+      </c>
+      <c r="IP2" t="n">
+        <v>997684</v>
+      </c>
+      <c r="IQ2" t="n">
+        <v>1227803</v>
+      </c>
+      <c r="IR2" t="n">
+        <v>663410</v>
+      </c>
+      <c r="IS2" t="n">
+        <v>409029</v>
+      </c>
+      <c r="IT2" t="n">
+        <v>169692</v>
+      </c>
+      <c r="IU2" t="n">
+        <v>44570</v>
+      </c>
+      <c r="IV2" t="n">
+        <v>801055</v>
+      </c>
+      <c r="IW2" t="n">
+        <v>72676</v>
+      </c>
+      <c r="IX2" t="n">
+        <v>679746</v>
+      </c>
+      <c r="IY2" t="n">
+        <v>736427</v>
+      </c>
+      <c r="IZ2" t="n">
+        <v>609402</v>
+      </c>
+      <c r="JA2" t="n">
+        <v>207272</v>
+      </c>
+      <c r="JB2" t="n">
+        <v>258116</v>
+      </c>
+      <c r="JC2" t="n">
+        <v>1104417</v>
+      </c>
+      <c r="JD2" t="n">
+        <v>819347</v>
+      </c>
+      <c r="JE2" t="n">
+        <v>865619</v>
+      </c>
+      <c r="JF2" t="n">
+        <v>473403</v>
+      </c>
+      <c r="JG2" t="n">
+        <v>292420</v>
+      </c>
+      <c r="JH2" t="n">
+        <v>621202</v>
+      </c>
+      <c r="JI2" t="n">
+        <v>184067</v>
+      </c>
+      <c r="JJ2" t="n">
+        <v>1138351</v>
+      </c>
+      <c r="JK2" t="n">
+        <v>358391</v>
+      </c>
+      <c r="JL2" t="n">
+        <v>267133</v>
+      </c>
+      <c r="JM2" t="n">
+        <v>469907</v>
+      </c>
+      <c r="JN2" t="n">
+        <v>266196</v>
+      </c>
+      <c r="JO2" t="n">
+        <v>40267</v>
+      </c>
+      <c r="JP2" t="n">
+        <v>1143302</v>
+      </c>
+      <c r="JQ2" t="n">
+        <v>328934</v>
+      </c>
+      <c r="JR2" t="n">
+        <v>1132267</v>
+      </c>
+      <c r="JS2" t="n">
+        <v>870017</v>
+      </c>
+      <c r="JT2" t="n">
+        <v>760531</v>
+      </c>
+      <c r="JU2" t="n">
+        <v>825370</v>
+      </c>
+      <c r="JV2" t="n">
+        <v>347794</v>
+      </c>
+      <c r="JW2" t="n">
+        <v>931526</v>
+      </c>
+      <c r="JX2" t="n">
+        <v>754581</v>
+      </c>
+      <c r="JY2" t="n">
+        <v>1161570</v>
+      </c>
+      <c r="JZ2" t="n">
+        <v>74147</v>
+      </c>
+      <c r="KA2" t="n">
+        <v>584177</v>
+      </c>
+      <c r="KB2" t="n">
+        <v>232081</v>
+      </c>
+      <c r="KC2" t="n">
+        <v>702261</v>
+      </c>
+      <c r="KD2" t="n">
+        <v>103957</v>
+      </c>
+      <c r="KE2" t="n">
+        <v>1161742</v>
+      </c>
+      <c r="KF2" t="n">
+        <v>786438</v>
+      </c>
+      <c r="KG2" t="n">
+        <v>251416</v>
+      </c>
+      <c r="KH2" t="n">
+        <v>951415</v>
+      </c>
+      <c r="KI2" t="n">
+        <v>591973</v>
+      </c>
+      <c r="KJ2" t="n">
+        <v>874064</v>
+      </c>
+      <c r="KK2" t="n">
+        <v>1027940</v>
+      </c>
+      <c r="KL2" t="n">
+        <v>1071979</v>
+      </c>
+      <c r="KM2" t="n">
+        <v>949828</v>
+      </c>
+      <c r="KN2" t="n">
+        <v>310400</v>
+      </c>
+      <c r="KO2" t="n">
+        <v>561057</v>
+      </c>
+      <c r="KP2" t="n">
+        <v>123626</v>
+      </c>
+      <c r="KQ2" t="n">
+        <v>1126904</v>
+      </c>
+      <c r="KR2" t="n">
+        <v>93724</v>
+      </c>
+      <c r="KS2" t="n">
+        <v>97634</v>
+      </c>
+      <c r="KT2" t="n">
+        <v>1114643</v>
+      </c>
+      <c r="KU2" t="n">
+        <v>80253</v>
+      </c>
+      <c r="KV2" t="n">
+        <v>711048</v>
+      </c>
+      <c r="KW2" t="n">
+        <v>140289</v>
+      </c>
+      <c r="KX2" t="n">
+        <v>542953</v>
+      </c>
+      <c r="KY2" t="n">
+        <v>957493</v>
+      </c>
+      <c r="KZ2" t="n">
+        <v>861002</v>
+      </c>
+      <c r="LA2" t="n">
+        <v>194527</v>
+      </c>
+      <c r="LB2" t="n">
+        <v>23131</v>
+      </c>
+      <c r="LC2" t="n">
+        <v>745313</v>
+      </c>
+      <c r="LD2" t="n">
+        <v>1200101</v>
+      </c>
+      <c r="LE2" t="n">
+        <v>888909</v>
+      </c>
+      <c r="LF2" t="n">
+        <v>494799</v>
+      </c>
+      <c r="LG2" t="n">
+        <v>1036621</v>
+      </c>
+      <c r="LH2" t="n">
+        <v>34948</v>
+      </c>
+      <c r="LI2" t="n">
+        <v>1134725</v>
+      </c>
+      <c r="LJ2" t="n">
+        <v>119664</v>
+      </c>
+      <c r="LK2" t="n">
+        <v>35350</v>
+      </c>
+      <c r="LL2" t="n">
+        <v>320655</v>
+      </c>
+      <c r="LM2" t="n">
+        <v>297148</v>
+      </c>
+      <c r="LN2" t="n">
+        <v>1199251</v>
+      </c>
+      <c r="LO2" t="n">
+        <v>396460</v>
+      </c>
+      <c r="LP2" t="n">
+        <v>68414</v>
+      </c>
+      <c r="LQ2" t="n">
+        <v>805220</v>
+      </c>
+      <c r="LR2" t="n">
+        <v>295114</v>
+      </c>
+      <c r="LS2" t="n">
+        <v>84690</v>
+      </c>
+      <c r="LT2" t="n">
+        <v>492438</v>
+      </c>
+      <c r="LU2" t="n">
+        <v>977159</v>
+      </c>
+      <c r="LV2" t="n">
+        <v>1062314</v>
+      </c>
+      <c r="LW2" t="n">
+        <v>331937</v>
+      </c>
+      <c r="LX2" t="n">
+        <v>933505</v>
+      </c>
+      <c r="LY2" t="n">
+        <v>20957</v>
+      </c>
+      <c r="LZ2" t="n">
+        <v>60228</v>
+      </c>
+      <c r="MA2" t="n">
+        <v>1081648</v>
+      </c>
+      <c r="MB2" t="n">
+        <v>629852</v>
+      </c>
+      <c r="MC2" t="n">
+        <v>1118731</v>
+      </c>
+      <c r="MD2" t="n">
+        <v>481843</v>
+      </c>
+      <c r="ME2" t="n">
+        <v>225713</v>
+      </c>
+      <c r="MF2" t="n">
+        <v>1152882</v>
+      </c>
+      <c r="MG2" t="n">
+        <v>216984</v>
+      </c>
+      <c r="MH2" t="n">
+        <v>1039124</v>
+      </c>
+      <c r="MI2" t="n">
+        <v>514118</v>
+      </c>
+      <c r="MJ2" t="n">
+        <v>305488</v>
+      </c>
+      <c r="MK2" t="n">
+        <v>983147</v>
+      </c>
+      <c r="ML2" t="n">
+        <v>1159942</v>
+      </c>
+      <c r="MM2" t="n">
+        <v>288020</v>
+      </c>
+      <c r="MN2" t="n">
+        <v>774176</v>
+      </c>
+      <c r="MO2" t="n">
+        <v>991906</v>
+      </c>
+      <c r="MP2" t="n">
+        <v>430979</v>
+      </c>
+      <c r="MQ2" t="n">
+        <v>970567</v>
+      </c>
+      <c r="MR2" t="n">
+        <v>1060983</v>
+      </c>
+      <c r="MS2" t="n">
+        <v>671550</v>
+      </c>
+      <c r="MT2" t="n">
+        <v>147974</v>
+      </c>
+      <c r="MU2" t="n">
+        <v>143453</v>
+      </c>
+      <c r="MV2" t="n">
+        <v>238957</v>
+      </c>
+      <c r="MW2" t="n">
+        <v>972565</v>
+      </c>
+      <c r="MX2" t="n">
+        <v>618610</v>
+      </c>
+      <c r="MY2" t="n">
+        <v>629106</v>
+      </c>
+      <c r="MZ2" t="n">
+        <v>971219</v>
+      </c>
+      <c r="NA2" t="n">
+        <v>517752</v>
+      </c>
+      <c r="NB2" t="n">
+        <v>304581</v>
+      </c>
+      <c r="NC2" t="n">
+        <v>377695</v>
+      </c>
+      <c r="ND2" t="n">
+        <v>634986</v>
+      </c>
+      <c r="NE2" t="n">
+        <v>935027</v>
+      </c>
+      <c r="NF2" t="n">
+        <v>161052</v>
+      </c>
+      <c r="NG2" t="n">
+        <v>264850</v>
+      </c>
+      <c r="NH2" t="n">
+        <v>411829</v>
+      </c>
+      <c r="NI2" t="n">
+        <v>931449</v>
+      </c>
+      <c r="NJ2" t="n">
+        <v>792891</v>
+      </c>
+      <c r="NK2" t="n">
+        <v>31079</v>
+      </c>
+      <c r="NL2" t="n">
+        <v>509162</v>
+      </c>
+      <c r="NM2" t="n">
+        <v>1057771</v>
+      </c>
+      <c r="NN2" t="n">
+        <v>436441</v>
+      </c>
+      <c r="NO2" t="n">
+        <v>840941</v>
+      </c>
+      <c r="NP2" t="n">
+        <v>894435</v>
+      </c>
+      <c r="NQ2" t="n">
+        <v>108491</v>
+      </c>
+      <c r="NR2" t="n">
+        <v>1188545</v>
+      </c>
+      <c r="NS2" t="n">
+        <v>132515</v>
+      </c>
+      <c r="NT2" t="n">
+        <v>1174374</v>
+      </c>
+      <c r="NU2" t="n">
+        <v>477484</v>
+      </c>
+      <c r="NV2" t="n">
+        <v>811457</v>
+      </c>
+      <c r="NW2" t="n">
+        <v>394</v>
+      </c>
+      <c r="NX2" t="n">
+        <v>166418</v>
+      </c>
+      <c r="NY2" t="n">
+        <v>85187</v>
+      </c>
+      <c r="NZ2" t="n">
+        <v>715162</v>
+      </c>
+      <c r="OA2" t="n">
+        <v>755101</v>
+      </c>
+      <c r="OB2" t="n">
+        <v>685342</v>
+      </c>
+      <c r="OC2" t="n">
+        <v>221299</v>
+      </c>
+      <c r="OD2" t="n">
+        <v>517794</v>
+      </c>
+      <c r="OE2" t="n">
+        <v>1000439</v>
+      </c>
+      <c r="OF2" t="n">
+        <v>1113714</v>
+      </c>
+      <c r="OG2" t="n">
+        <v>319752</v>
+      </c>
+      <c r="OH2" t="n">
+        <v>118783</v>
+      </c>
+      <c r="OI2" t="n">
+        <v>945786</v>
+      </c>
+      <c r="OJ2" t="n">
+        <v>146578</v>
+      </c>
+      <c r="OK2" t="n">
+        <v>1016524</v>
+      </c>
+      <c r="OL2" t="n">
+        <v>950062</v>
+      </c>
+      <c r="OM2" t="n">
+        <v>747453</v>
+      </c>
+      <c r="ON2" t="n">
+        <v>1187170</v>
+      </c>
+      <c r="OO2" t="n">
+        <v>96779</v>
+      </c>
+      <c r="OP2" t="n">
+        <v>510287</v>
+      </c>
+      <c r="OQ2" t="n">
+        <v>873634</v>
+      </c>
+      <c r="OR2" t="n">
+        <v>940621</v>
+      </c>
+      <c r="OS2" t="n">
+        <v>320106</v>
+      </c>
+      <c r="OT2" t="n">
+        <v>662844</v>
+      </c>
+      <c r="OU2" t="n">
+        <v>300749</v>
+      </c>
+      <c r="OV2" t="n">
+        <v>634129</v>
+      </c>
+      <c r="OW2" t="n">
+        <v>632290</v>
+      </c>
+      <c r="OX2" t="n">
+        <v>993336</v>
+      </c>
+      <c r="OY2" t="n">
+        <v>153022</v>
+      </c>
+      <c r="OZ2" t="n">
+        <v>721622</v>
+      </c>
+      <c r="PA2" t="n">
+        <v>918373</v>
+      </c>
+      <c r="PB2" t="n">
+        <v>848630</v>
+      </c>
+      <c r="PC2" t="n">
+        <v>856453</v>
+      </c>
+      <c r="PD2" t="n">
+        <v>503184</v>
+      </c>
+      <c r="PE2" t="n">
+        <v>531218</v>
+      </c>
+      <c r="PF2" t="n">
+        <v>1054794</v>
+      </c>
+      <c r="PG2" t="n">
+        <v>984195</v>
+      </c>
+      <c r="PH2" t="n">
+        <v>20937</v>
+      </c>
+      <c r="PI2" t="n">
+        <v>462924</v>
+      </c>
+      <c r="PJ2" t="n">
+        <v>239490</v>
+      </c>
+      <c r="PK2" t="n">
+        <v>837002</v>
+      </c>
+      <c r="PL2" t="n">
+        <v>1217411</v>
+      </c>
+      <c r="PM2" t="n">
+        <v>1109525</v>
+      </c>
+      <c r="PN2" t="n">
+        <v>1996</v>
+      </c>
+      <c r="PO2" t="n">
+        <v>922850</v>
+      </c>
+      <c r="PP2" t="n">
+        <v>283418</v>
+      </c>
+      <c r="PQ2" t="n">
+        <v>1208982</v>
+      </c>
+      <c r="PR2" t="n">
+        <v>1044470</v>
+      </c>
+      <c r="PS2" t="n">
+        <v>432189</v>
+      </c>
+      <c r="PT2" t="n">
+        <v>374406</v>
+      </c>
+      <c r="PU2" t="n">
+        <v>272911</v>
+      </c>
+      <c r="PV2" t="n">
+        <v>625920</v>
+      </c>
+      <c r="PW2" t="n">
+        <v>483700</v>
+      </c>
+      <c r="PX2" t="n">
+        <v>499668</v>
+      </c>
+      <c r="PY2" t="n">
+        <v>214259</v>
+      </c>
+      <c r="PZ2" t="n">
+        <v>776510</v>
+      </c>
+      <c r="QA2" t="n">
+        <v>574127</v>
+      </c>
+      <c r="QB2" t="n">
+        <v>600015</v>
+      </c>
+      <c r="QC2" t="n">
+        <v>998304</v>
+      </c>
+      <c r="QD2" t="n">
+        <v>381329</v>
+      </c>
+      <c r="QE2" t="n">
+        <v>978530</v>
+      </c>
+      <c r="QF2" t="n">
+        <v>170729</v>
+      </c>
+      <c r="QG2" t="n">
+        <v>413964</v>
+      </c>
+      <c r="QH2" t="n">
+        <v>348408</v>
+      </c>
+      <c r="QI2" t="n">
+        <v>386086</v>
+      </c>
+      <c r="QJ2" t="n">
+        <v>1033353</v>
+      </c>
+      <c r="QK2" t="n">
+        <v>88031</v>
+      </c>
+      <c r="QL2" t="n">
+        <v>589355</v>
+      </c>
+      <c r="QM2" t="n">
+        <v>619237</v>
+      </c>
+      <c r="QN2" t="n">
+        <v>223761</v>
+      </c>
+      <c r="QO2" t="n">
+        <v>140143</v>
+      </c>
+      <c r="QP2" t="n">
+        <v>152439</v>
+      </c>
+      <c r="QQ2" t="n">
+        <v>1053073</v>
+      </c>
+      <c r="QR2" t="n">
+        <v>898162</v>
+      </c>
+      <c r="QS2" t="n">
+        <v>359215</v>
+      </c>
+      <c r="QT2" t="n">
+        <v>545849</v>
+      </c>
+      <c r="QU2" t="n">
+        <v>1066350</v>
+      </c>
+      <c r="QV2" t="n">
+        <v>695083</v>
+      </c>
+      <c r="QW2" t="n">
+        <v>17567</v>
+      </c>
+      <c r="QX2" t="n">
+        <v>641905</v>
+      </c>
+      <c r="QY2" t="n">
+        <v>233508</v>
+      </c>
+      <c r="QZ2" t="n">
+        <v>833854</v>
+      </c>
+      <c r="RA2" t="n">
+        <v>1139331</v>
+      </c>
+      <c r="RB2" t="n">
+        <v>880844</v>
+      </c>
+      <c r="RC2" t="n">
+        <v>223937</v>
+      </c>
+      <c r="RD2" t="n">
+        <v>1023085</v>
+      </c>
+      <c r="RE2" t="n">
+        <v>86521</v>
+      </c>
+      <c r="RF2" t="n">
+        <v>595353</v>
+      </c>
+      <c r="RG2" t="n">
+        <v>211187</v>
+      </c>
+      <c r="RH2" t="n">
+        <v>963590</v>
+      </c>
+      <c r="RI2" t="n">
+        <v>723308</v>
+      </c>
+      <c r="RJ2" t="n">
+        <v>273145</v>
+      </c>
+      <c r="RK2" t="n">
+        <v>667864</v>
+      </c>
+      <c r="RL2" t="n">
+        <v>33528</v>
+      </c>
+      <c r="RM2" t="n">
+        <v>181213</v>
+      </c>
+      <c r="RN2" t="n">
+        <v>521989</v>
+      </c>
+      <c r="RO2" t="n">
+        <v>342012</v>
+      </c>
+      <c r="RP2" t="n">
+        <v>1003493</v>
+      </c>
+      <c r="RQ2" t="n">
+        <v>445361</v>
+      </c>
+      <c r="RR2" t="n">
+        <v>884246</v>
+      </c>
+      <c r="RS2" t="n">
+        <v>601539</v>
+      </c>
+      <c r="RT2" t="n">
+        <v>55317</v>
+      </c>
+      <c r="RU2" t="n">
+        <v>123668</v>
+      </c>
+      <c r="RV2" t="n">
+        <v>51757</v>
+      </c>
+      <c r="RW2" t="n">
+        <v>864560</v>
+      </c>
+      <c r="RX2" t="n">
+        <v>16283</v>
+      </c>
+      <c r="RY2" t="n">
+        <v>875078</v>
+      </c>
+      <c r="RZ2" t="n">
+        <v>941979</v>
+      </c>
+      <c r="SA2" t="n">
+        <v>693852</v>
+      </c>
+      <c r="SB2" t="n">
+        <v>326939</v>
+      </c>
+      <c r="SC2" t="n">
+        <v>1073277</v>
+      </c>
+      <c r="SD2" t="n">
+        <v>10201</v>
+      </c>
+      <c r="SE2" t="n">
+        <v>1129219</v>
+      </c>
+      <c r="SF2" t="n">
+        <v>469465</v>
+      </c>
+      <c r="SG2" t="n">
+        <v>650528</v>
+      </c>
+      <c r="SH2" t="n">
+        <v>199006</v>
+      </c>
+      <c r="SI2" t="n">
+        <v>560700</v>
+      </c>
+      <c r="SJ2" t="n">
+        <v>365322</v>
+      </c>
+      <c r="SK2" t="n">
+        <v>653244</v>
+      </c>
+      <c r="SL2" t="n">
+        <v>489381</v>
+      </c>
+      <c r="SM2" t="n">
+        <v>707892</v>
+      </c>
+      <c r="SN2" t="n">
+        <v>402705</v>
+      </c>
+      <c r="SO2" t="n">
+        <v>1132770</v>
+      </c>
+      <c r="SP2" t="n">
+        <v>334498</v>
+      </c>
+      <c r="SQ2" t="n">
+        <v>575651</v>
+      </c>
+      <c r="SR2" t="n">
+        <v>178080</v>
+      </c>
+      <c r="SS2" t="n">
+        <v>107163</v>
+      </c>
+      <c r="ST2" t="n">
+        <v>132155</v>
+      </c>
+      <c r="SU2" t="n">
+        <v>464344</v>
+      </c>
+      <c r="SV2" t="n">
+        <v>859050</v>
+      </c>
+      <c r="SW2" t="n">
+        <v>1205606</v>
+      </c>
+      <c r="SX2" t="n">
+        <v>735961</v>
+      </c>
+      <c r="SY2" t="n">
+        <v>848825</v>
+      </c>
+      <c r="SZ2" t="n">
+        <v>1020039</v>
+      </c>
+      <c r="TA2" t="n">
+        <v>77739</v>
+      </c>
+      <c r="TB2" t="n">
+        <v>764900</v>
+      </c>
+      <c r="TC2" t="n">
+        <v>133956</v>
+      </c>
+      <c r="TD2" t="n">
+        <v>370282</v>
+      </c>
+      <c r="TE2" t="n">
+        <v>447208</v>
+      </c>
+      <c r="TF2" t="n">
+        <v>277310</v>
+      </c>
+      <c r="TG2" t="n">
+        <v>241298</v>
+      </c>
+      <c r="TH2" t="n">
+        <v>1077907</v>
+      </c>
+      <c r="TI2" t="n">
+        <v>738950</v>
+      </c>
+      <c r="TJ2" t="n">
+        <v>381789</v>
+      </c>
+      <c r="TK2" t="n">
+        <v>795959</v>
+      </c>
+      <c r="TL2" t="n">
+        <v>67001</v>
+      </c>
+      <c r="TM2" t="n">
+        <v>166104</v>
+      </c>
+      <c r="TN2" t="n">
+        <v>331055</v>
+      </c>
+      <c r="TO2" t="n">
+        <v>20348</v>
+      </c>
+      <c r="TP2" t="n">
+        <v>352011</v>
+      </c>
+      <c r="TQ2" t="n">
+        <v>1047881</v>
+      </c>
+      <c r="TR2" t="n">
+        <v>890171</v>
+      </c>
+      <c r="TS2" t="n">
+        <v>428617</v>
+      </c>
+      <c r="TT2" t="n">
+        <v>59505</v>
+      </c>
+      <c r="TU2" t="n">
+        <v>438206</v>
+      </c>
+      <c r="TV2" t="n">
+        <v>917121</v>
+      </c>
+      <c r="TW2" t="n">
+        <v>987370</v>
+      </c>
+      <c r="TX2" t="n">
+        <v>532732</v>
+      </c>
+      <c r="TY2" t="n">
+        <v>663716</v>
+      </c>
+      <c r="TZ2" t="n">
+        <v>76345</v>
+      </c>
+      <c r="UA2" t="n">
+        <v>558235</v>
+      </c>
+      <c r="UB2" t="n">
+        <v>638223</v>
+      </c>
+      <c r="UC2" t="n">
+        <v>608324</v>
+      </c>
+      <c r="UD2" t="n">
+        <v>19213</v>
+      </c>
+      <c r="UE2" t="n">
+        <v>392366</v>
+      </c>
+      <c r="UF2" t="n">
+        <v>496111</v>
+      </c>
+      <c r="UG2" t="n">
+        <v>595145</v>
+      </c>
+      <c r="UH2" t="n">
+        <v>1007893</v>
+      </c>
+      <c r="UI2" t="n">
+        <v>612782</v>
+      </c>
+      <c r="UJ2" t="n">
+        <v>57093</v>
+      </c>
+      <c r="UK2" t="n">
+        <v>453609</v>
+      </c>
+      <c r="UL2" t="n">
+        <v>385334</v>
+      </c>
+      <c r="UM2" t="n">
+        <v>840314</v>
+      </c>
+      <c r="UN2" t="n">
+        <v>421531</v>
+      </c>
+      <c r="UO2" t="n">
+        <v>485677</v>
+      </c>
+      <c r="UP2" t="n">
+        <v>172668</v>
+      </c>
+      <c r="UQ2" t="n">
+        <v>1038485</v>
+      </c>
+      <c r="UR2" t="n">
+        <v>575861</v>
+      </c>
+      <c r="US2" t="n">
+        <v>672124</v>
+      </c>
+      <c r="UT2" t="n">
+        <v>967038</v>
+      </c>
+      <c r="UU2" t="n">
+        <v>216128</v>
+      </c>
+      <c r="UV2" t="n">
+        <v>596605</v>
+      </c>
+      <c r="UW2" t="n">
+        <v>1141322</v>
+      </c>
+      <c r="UX2" t="n">
+        <v>879502</v>
+      </c>
+      <c r="UY2" t="n">
+        <v>276045</v>
+      </c>
+      <c r="UZ2" t="n">
+        <v>612900</v>
+      </c>
+      <c r="VA2" t="n">
+        <v>1213646</v>
+      </c>
+      <c r="VB2" t="n">
+        <v>749758</v>
+      </c>
+      <c r="VC2" t="n">
+        <v>709144</v>
+      </c>
+      <c r="VD2" t="n">
+        <v>842964</v>
+      </c>
+      <c r="VE2" t="n">
+        <v>733580</v>
+      </c>
+      <c r="VF2" t="n">
+        <v>24972</v>
+      </c>
+      <c r="VG2" t="n">
+        <v>238749</v>
+      </c>
+      <c r="VH2" t="n">
+        <v>448107</v>
+      </c>
+      <c r="VI2" t="n">
+        <v>826526</v>
+      </c>
+      <c r="VJ2" t="n">
+        <v>644989</v>
+      </c>
+      <c r="VK2" t="n">
+        <v>247202</v>
+      </c>
+      <c r="VL2" t="n">
+        <v>1157946</v>
+      </c>
+      <c r="VM2" t="n">
+        <v>81078</v>
+      </c>
+      <c r="VN2" t="n">
+        <v>69848</v>
+      </c>
+      <c r="VO2" t="n">
+        <v>1168931</v>
+      </c>
+      <c r="VP2" t="n">
+        <v>876424</v>
+      </c>
+      <c r="VQ2" t="n">
+        <v>11563</v>
+      </c>
+      <c r="VR2" t="n">
+        <v>473841</v>
+      </c>
+      <c r="VS2" t="n">
+        <v>480336</v>
+      </c>
+      <c r="VT2" t="n">
+        <v>845155</v>
+      </c>
+      <c r="VU2" t="n">
+        <v>110800</v>
+      </c>
+      <c r="VV2" t="n">
+        <v>996297</v>
+      </c>
+      <c r="VW2" t="n">
+        <v>547973</v>
+      </c>
+      <c r="VX2" t="n">
+        <v>693964</v>
+      </c>
+      <c r="VY2" t="n">
+        <v>356604</v>
+      </c>
+      <c r="VZ2" t="n">
+        <v>910142</v>
+      </c>
+      <c r="WA2" t="n">
+        <v>1208335</v>
+      </c>
+      <c r="WB2" t="n">
+        <v>436185</v>
+      </c>
+      <c r="WC2" t="n">
+        <v>474587</v>
+      </c>
+      <c r="WD2" t="n">
+        <v>570155</v>
+      </c>
+      <c r="WE2" t="n">
+        <v>1049297</v>
+      </c>
+      <c r="WF2" t="n">
+        <v>405730</v>
+      </c>
+      <c r="WG2" t="n">
+        <v>914327</v>
+      </c>
+      <c r="WH2" t="n">
+        <v>516472</v>
+      </c>
+      <c r="WI2" t="n">
+        <v>345049</v>
+      </c>
+      <c r="WJ2" t="n">
+        <v>423947</v>
+      </c>
+      <c r="WK2" t="n">
+        <v>959905</v>
+      </c>
+      <c r="WL2" t="n">
+        <v>1062620</v>
+      </c>
+      <c r="WM2" t="n">
+        <v>771664</v>
+      </c>
+      <c r="WN2" t="n">
+        <v>423596</v>
+      </c>
+      <c r="WO2" t="n">
+        <v>1064897</v>
+      </c>
+      <c r="WP2" t="n">
+        <v>349637</v>
+      </c>
+      <c r="WQ2" t="n">
+        <v>701051</v>
+      </c>
+      <c r="WR2" t="n">
+        <v>1135851</v>
+      </c>
+      <c r="WS2" t="n">
+        <v>885933</v>
+      </c>
+      <c r="WT2" t="n">
+        <v>390678</v>
+      </c>
+      <c r="WU2" t="n">
+        <v>672342</v>
+      </c>
+      <c r="WV2" t="n">
+        <v>8330</v>
+      </c>
+      <c r="WW2" t="n">
+        <v>420685</v>
+      </c>
+      <c r="WX2" t="n">
+        <v>461094</v>
+      </c>
+      <c r="WY2" t="n">
+        <v>1104205</v>
+      </c>
+      <c r="WZ2" t="n">
+        <v>409066</v>
+      </c>
+      <c r="XA2" t="n">
+        <v>870944</v>
+      </c>
+      <c r="XB2" t="n">
+        <v>373359</v>
+      </c>
+      <c r="XC2" t="n">
+        <v>300137</v>
+      </c>
+      <c r="XD2" t="n">
+        <v>162089</v>
+      </c>
+      <c r="XE2" t="n">
+        <v>287898</v>
+      </c>
+      <c r="XF2" t="n">
+        <v>547947</v>
+      </c>
+      <c r="XG2" t="n">
+        <v>535110</v>
+      </c>
+      <c r="XH2" t="n">
+        <v>344199</v>
+      </c>
+      <c r="XI2" t="n">
+        <v>1005445</v>
+      </c>
+      <c r="XJ2" t="n">
+        <v>610963</v>
+      </c>
+      <c r="XK2" t="n">
+        <v>311778</v>
+      </c>
+      <c r="XL2" t="n">
+        <v>425982</v>
+      </c>
+      <c r="XM2" t="n">
+        <v>1210321</v>
+      </c>
+      <c r="XN2" t="n">
+        <v>64024</v>
+      </c>
+      <c r="XO2" t="n">
+        <v>655967</v>
+      </c>
+      <c r="XP2" t="n">
+        <v>642161</v>
+      </c>
+      <c r="XQ2" t="n">
+        <v>940203</v>
+      </c>
+      <c r="XR2" t="n">
+        <v>731600</v>
+      </c>
+      <c r="XS2" t="n">
+        <v>513860</v>
+      </c>
+      <c r="XT2" t="n">
+        <v>795713</v>
+      </c>
+      <c r="XU2" t="n">
+        <v>441096</v>
+      </c>
+      <c r="XV2" t="n">
+        <v>281449</v>
+      </c>
+      <c r="XW2" t="n">
+        <v>1175220</v>
+      </c>
+      <c r="XX2" t="n">
+        <v>937261</v>
+      </c>
+      <c r="XY2" t="n">
+        <v>1144510</v>
+      </c>
+      <c r="XZ2" t="n">
+        <v>91684</v>
+      </c>
+      <c r="YA2" t="n">
+        <v>478888</v>
+      </c>
+      <c r="YB2" t="n">
+        <v>261013</v>
+      </c>
+      <c r="YC2" t="n">
+        <v>674405</v>
+      </c>
+      <c r="YD2" t="n">
+        <v>765732</v>
+      </c>
+      <c r="YE2" t="n">
+        <v>56676</v>
+      </c>
+      <c r="YF2" t="n">
+        <v>29181</v>
+      </c>
+      <c r="YG2" t="n">
+        <v>868085</v>
+      </c>
+      <c r="YH2" t="n">
+        <v>235230</v>
+      </c>
+      <c r="YI2" t="n">
+        <v>102469</v>
+      </c>
+      <c r="YJ2" t="n">
+        <v>484741</v>
+      </c>
+      <c r="YK2" t="n">
+        <v>268368</v>
+      </c>
+      <c r="YL2" t="n">
+        <v>1096308</v>
+      </c>
+      <c r="YM2" t="n">
+        <v>291864</v>
+      </c>
+      <c r="YN2" t="n">
+        <v>41120</v>
+      </c>
+      <c r="YO2" t="n">
+        <v>322587</v>
+      </c>
+      <c r="YP2" t="n">
+        <v>630692</v>
+      </c>
+      <c r="YQ2" t="n">
+        <v>279763</v>
+      </c>
+      <c r="YR2" t="n">
+        <v>368232</v>
+      </c>
+      <c r="YS2" t="n">
+        <v>919538</v>
+      </c>
+      <c r="YT2" t="n">
+        <v>987583</v>
+      </c>
+      <c r="YU2" t="n">
+        <v>244566</v>
+      </c>
+      <c r="YV2" t="n">
+        <v>1032537</v>
+      </c>
+      <c r="YW2" t="n">
+        <v>747311</v>
+      </c>
+      <c r="YX2" t="n">
+        <v>788541</v>
+      </c>
+      <c r="YY2" t="n">
+        <v>1053917</v>
+      </c>
+      <c r="YZ2" t="n">
+        <v>1057266</v>
+      </c>
+      <c r="ZA2" t="n">
+        <v>1051096</v>
+      </c>
+      <c r="ZB2" t="n">
+        <v>582155</v>
+      </c>
+      <c r="ZC2" t="n">
+        <v>172803</v>
+      </c>
+      <c r="ZD2" t="n">
+        <v>694507</v>
+      </c>
+      <c r="ZE2" t="n">
+        <v>419656</v>
+      </c>
+      <c r="ZF2" t="n">
+        <v>437061</v>
+      </c>
+      <c r="ZG2" t="n">
+        <v>256319</v>
+      </c>
+      <c r="ZH2" t="n">
+        <v>1017332</v>
+      </c>
+      <c r="ZI2" t="n">
+        <v>232233</v>
+      </c>
+      <c r="ZJ2" t="n">
+        <v>362383</v>
+      </c>
+      <c r="ZK2" t="n">
+        <v>467595</v>
+      </c>
+      <c r="ZL2" t="n">
+        <v>397031</v>
+      </c>
+      <c r="ZM2" t="n">
+        <v>460871</v>
+      </c>
+      <c r="ZN2" t="n">
+        <v>324743</v>
+      </c>
+      <c r="ZO2" t="n">
+        <v>445030</v>
+      </c>
+      <c r="ZP2" t="n">
+        <v>1121932</v>
+      </c>
+      <c r="ZQ2" t="n">
+        <v>429484</v>
+      </c>
+      <c r="ZR2" t="n">
+        <v>127215</v>
+      </c>
+      <c r="ZS2" t="n">
+        <v>561305</v>
+      </c>
+      <c r="ZT2" t="n">
+        <v>511659</v>
+      </c>
+      <c r="ZU2" t="n">
+        <v>279149</v>
+      </c>
+      <c r="ZV2" t="n">
+        <v>406654</v>
+      </c>
+      <c r="ZW2" t="n">
+        <v>454991</v>
+      </c>
+      <c r="ZX2" t="n">
+        <v>330582</v>
+      </c>
+      <c r="ZY2" t="n">
+        <v>657630</v>
+      </c>
+      <c r="ZZ2" t="n">
+        <v>389969</v>
+      </c>
+      <c r="AAA2" t="n">
+        <v>1117706</v>
+      </c>
+      <c r="AAB2" t="n">
+        <v>264860</v>
+      </c>
+      <c r="AAC2" t="n">
+        <v>306311</v>
+      </c>
+      <c r="AAD2" t="n">
+        <v>124579</v>
+      </c>
+      <c r="AAE2" t="n">
+        <v>881254</v>
+      </c>
+      <c r="AAF2" t="n">
+        <v>847038</v>
+      </c>
+      <c r="AAG2" t="n">
+        <v>273884</v>
+      </c>
+      <c r="AAH2" t="n">
+        <v>242193</v>
+      </c>
+      <c r="AAI2" t="n">
+        <v>43454</v>
+      </c>
+      <c r="AAJ2" t="n">
+        <v>1184428</v>
+      </c>
+      <c r="AAK2" t="n">
+        <v>717586</v>
+      </c>
+      <c r="AAL2" t="n">
+        <v>648510</v>
+      </c>
+      <c r="AAM2" t="n">
+        <v>83484</v>
+      </c>
+      <c r="AAN2" t="n">
+        <v>214965</v>
+      </c>
+      <c r="AAO2" t="n">
+        <v>1012882</v>
+      </c>
+      <c r="AAP2" t="n">
+        <v>179399</v>
+      </c>
+      <c r="AAQ2" t="n">
+        <v>955153</v>
+      </c>
+      <c r="AAR2" t="n">
+        <v>745265</v>
+      </c>
+      <c r="AAS2" t="n">
+        <v>163953</v>
+      </c>
+      <c r="AAT2" t="n">
+        <v>687883</v>
+      </c>
+      <c r="AAU2" t="n">
+        <v>1124273</v>
+      </c>
+      <c r="AAV2" t="n">
+        <v>226999</v>
+      </c>
+      <c r="AAW2" t="n">
+        <v>395588</v>
+      </c>
+      <c r="AAX2" t="n">
+        <v>1149158</v>
+      </c>
+      <c r="AAY2" t="n">
+        <v>378529</v>
+      </c>
+      <c r="AAZ2" t="n">
+        <v>208818</v>
+      </c>
+      <c r="ABA2" t="n">
+        <v>205656</v>
+      </c>
+      <c r="ABB2" t="n">
+        <v>527373</v>
+      </c>
+      <c r="ABC2" t="n">
+        <v>903401</v>
+      </c>
+      <c r="ABD2" t="n">
+        <v>398854</v>
+      </c>
+      <c r="ABE2" t="n">
+        <v>424462</v>
+      </c>
+      <c r="ABF2" t="n">
+        <v>600165</v>
+      </c>
+      <c r="ABG2" t="n">
+        <v>1121903</v>
+      </c>
+      <c r="ABH2" t="n">
+        <v>339677</v>
+      </c>
+      <c r="ABI2" t="n">
+        <v>43990</v>
+      </c>
+      <c r="ABJ2" t="n">
+        <v>3055</v>
+      </c>
+      <c r="ABK2" t="n">
+        <v>564902</v>
+      </c>
+      <c r="ABL2" t="n">
+        <v>615205</v>
+      </c>
+      <c r="ABM2" t="n">
+        <v>738875</v>
+      </c>
+      <c r="ABN2" t="n">
+        <v>285736</v>
+      </c>
+      <c r="ABO2" t="n">
+        <v>139023</v>
+      </c>
+      <c r="ABP2" t="n">
+        <v>411145</v>
+      </c>
+      <c r="ABQ2" t="n">
+        <v>927149</v>
+      </c>
+      <c r="ABR2" t="n">
+        <v>374420</v>
+      </c>
+      <c r="ABS2" t="n">
+        <v>289602</v>
+      </c>
+      <c r="ABT2" t="n">
+        <v>862255</v>
+      </c>
+      <c r="ABU2" t="n">
+        <v>752305</v>
+      </c>
+      <c r="ABV2" t="n">
+        <v>531463</v>
+      </c>
+      <c r="ABW2" t="n">
+        <v>887030</v>
+      </c>
+      <c r="ABX2" t="n">
+        <v>5419</v>
+      </c>
+      <c r="ABY2" t="n">
+        <v>164197</v>
+      </c>
+      <c r="ABZ2" t="n">
+        <v>465198</v>
+      </c>
+      <c r="ACA2" t="n">
+        <v>166070</v>
+      </c>
+      <c r="ACB2" t="n">
+        <v>654579</v>
+      </c>
+      <c r="ACC2" t="n">
+        <v>952123</v>
+      </c>
+      <c r="ACD2" t="n">
+        <v>920955</v>
+      </c>
+      <c r="ACE2" t="n">
+        <v>1195219</v>
+      </c>
+      <c r="ACF2" t="n">
+        <v>767107</v>
+      </c>
+      <c r="ACG2" t="n">
+        <v>260093</v>
+      </c>
+      <c r="ACH2" t="n">
+        <v>66593</v>
+      </c>
+      <c r="ACI2" t="n">
+        <v>1117137</v>
+      </c>
+      <c r="ACJ2" t="n">
+        <v>632217</v>
+      </c>
+      <c r="ACK2" t="n">
+        <v>205780</v>
+      </c>
+      <c r="ACL2" t="n">
+        <v>1024872</v>
+      </c>
+      <c r="ACM2" t="n">
+        <v>124263</v>
+      </c>
+      <c r="ACN2" t="n">
+        <v>372354</v>
+      </c>
+      <c r="ACO2" t="n">
+        <v>294085</v>
+      </c>
+      <c r="ACP2" t="n">
+        <v>158968</v>
+      </c>
+      <c r="ACQ2" t="n">
+        <v>137452</v>
+      </c>
+      <c r="ACR2" t="n">
+        <v>314838</v>
+      </c>
+      <c r="ACS2" t="n">
+        <v>293853</v>
+      </c>
+      <c r="ACT2" t="n">
+        <v>956399</v>
+      </c>
+      <c r="ACU2" t="n">
+        <v>789115</v>
+      </c>
+      <c r="ACV2" t="n">
+        <v>866892</v>
+      </c>
+      <c r="ACW2" t="n">
+        <v>1090620</v>
+      </c>
+      <c r="ACX2" t="n">
+        <v>507934</v>
+      </c>
+      <c r="ACY2" t="n">
+        <v>553261</v>
+      </c>
+      <c r="ACZ2" t="n">
+        <v>883678</v>
+      </c>
+      <c r="ADA2" t="n">
+        <v>228737</v>
+      </c>
+      <c r="ADB2" t="n">
+        <v>552559</v>
+      </c>
+      <c r="ADC2" t="n">
+        <v>726783</v>
+      </c>
+      <c r="ADD2" t="n">
+        <v>203181</v>
+      </c>
+      <c r="ADE2" t="n">
+        <v>191562</v>
+      </c>
+      <c r="ADF2" t="n">
+        <v>1177320</v>
+      </c>
+      <c r="ADG2" t="n">
+        <v>117338</v>
+      </c>
+      <c r="ADH2" t="n">
+        <v>758454</v>
+      </c>
+      <c r="ADI2" t="n">
+        <v>108310</v>
+      </c>
+      <c r="ADJ2" t="n">
+        <v>541119</v>
+      </c>
+      <c r="ADK2" t="n">
+        <v>414075</v>
+      </c>
+      <c r="ADL2" t="n">
+        <v>1006548</v>
+      </c>
+      <c r="ADM2" t="n">
+        <v>780768</v>
+      </c>
+      <c r="ADN2" t="n">
+        <v>96718</v>
+      </c>
+      <c r="ADO2" t="n">
+        <v>781790</v>
+      </c>
+      <c r="ADP2" t="n">
+        <v>540756</v>
+      </c>
+      <c r="ADQ2" t="n">
+        <v>541173</v>
+      </c>
+      <c r="ADR2" t="n">
+        <v>717301</v>
+      </c>
+      <c r="ADS2" t="n">
+        <v>61926</v>
+      </c>
+      <c r="ADT2" t="n">
+        <v>47760</v>
+      </c>
+      <c r="ADU2" t="n">
+        <v>1171252</v>
+      </c>
+      <c r="ADV2" t="n">
+        <v>585688</v>
+      </c>
+      <c r="ADW2" t="n">
+        <v>152704</v>
+      </c>
+      <c r="ADX2" t="n">
+        <v>1001835</v>
+      </c>
+      <c r="ADY2" t="n">
+        <v>978771</v>
+      </c>
+      <c r="ADZ2" t="n">
+        <v>795292</v>
+      </c>
+      <c r="AEA2" t="n">
+        <v>952768</v>
+      </c>
+      <c r="AEB2" t="n">
+        <v>263497</v>
+      </c>
+      <c r="AEC2" t="n">
+        <v>742125</v>
+      </c>
+      <c r="AED2" t="n">
+        <v>248167</v>
+      </c>
+      <c r="AEE2" t="n">
+        <v>150140</v>
+      </c>
+      <c r="AEF2" t="n">
+        <v>188081</v>
+      </c>
+      <c r="AEG2" t="n">
+        <v>900477</v>
+      </c>
+      <c r="AEH2" t="n">
+        <v>68779</v>
+      </c>
+      <c r="AEI2" t="n">
+        <v>145719</v>
+      </c>
+      <c r="AEJ2" t="n">
+        <v>1074454</v>
+      </c>
+      <c r="AEK2" t="n">
+        <v>442677</v>
+      </c>
+      <c r="AEL2" t="n">
+        <v>706232</v>
+      </c>
+      <c r="AEM2" t="n">
+        <v>432495</v>
+      </c>
+      <c r="AEN2" t="n">
+        <v>881925</v>
+      </c>
+      <c r="AEO2" t="n">
+        <v>309219</v>
+      </c>
+      <c r="AEP2" t="n">
+        <v>1127793</v>
+      </c>
+      <c r="AEQ2" t="n">
+        <v>1043892</v>
+      </c>
+      <c r="AER2" t="n">
+        <v>705172</v>
+      </c>
+      <c r="AES2" t="n">
+        <v>350880</v>
+      </c>
+      <c r="AET2" t="n">
+        <v>276240</v>
+      </c>
+      <c r="AEU2" t="n">
+        <v>125337</v>
+      </c>
+      <c r="AEV2" t="n">
+        <v>178415</v>
+      </c>
+      <c r="AEW2" t="n">
+        <v>911068</v>
+      </c>
+      <c r="AEX2" t="n">
+        <v>892583</v>
+      </c>
+      <c r="AEY2" t="n">
+        <v>820207</v>
+      </c>
+      <c r="AEZ2" t="n">
+        <v>982577</v>
+      </c>
+      <c r="AFA2" t="n">
+        <v>1255</v>
+      </c>
+      <c r="AFB2" t="n">
+        <v>474007</v>
+      </c>
+      <c r="AFC2" t="n">
+        <v>498701</v>
+      </c>
+      <c r="AFD2" t="n">
+        <v>234347</v>
+      </c>
+      <c r="AFE2" t="n">
+        <v>183181</v>
+      </c>
+      <c r="AFF2" t="n">
+        <v>1154901</v>
+      </c>
+      <c r="AFG2" t="n">
+        <v>112114</v>
+      </c>
+      <c r="AFH2" t="n">
+        <v>281220</v>
+      </c>
+      <c r="AFI2" t="n">
+        <v>249110</v>
+      </c>
+      <c r="AFJ2" t="n">
+        <v>590403</v>
+      </c>
+      <c r="AFK2" t="n">
+        <v>92528</v>
+      </c>
+      <c r="AFL2" t="n">
+        <v>1221335</v>
+      </c>
+      <c r="AFM2" t="n">
+        <v>708304</v>
+      </c>
+      <c r="AFN2" t="n">
+        <v>533679</v>
+      </c>
+      <c r="AFO2" t="n">
+        <v>740295</v>
+      </c>
+      <c r="AFP2" t="n">
+        <v>1094332</v>
+      </c>
+      <c r="AFQ2" t="n">
+        <v>489768</v>
+      </c>
+      <c r="AFR2" t="n">
+        <v>714969</v>
+      </c>
+      <c r="AFS2" t="n">
+        <v>284747</v>
+      </c>
+      <c r="AFT2" t="n">
+        <v>377148</v>
+      </c>
+      <c r="AFU2" t="n">
+        <v>195223</v>
+      </c>
+      <c r="AFV2" t="n">
+        <v>5746</v>
+      </c>
+      <c r="AFW2" t="n">
+        <v>807815</v>
+      </c>
+      <c r="AFX2" t="n">
+        <v>1224185</v>
+      </c>
+      <c r="AFY2" t="n">
+        <v>466793</v>
+      </c>
+      <c r="AFZ2" t="n">
+        <v>1008697</v>
+      </c>
+      <c r="AGA2" t="n">
+        <v>574409</v>
+      </c>
+      <c r="AGB2" t="n">
+        <v>584607</v>
+      </c>
+      <c r="AGC2" t="n">
+        <v>259250</v>
+      </c>
+      <c r="AGD2" t="n">
+        <v>185884</v>
+      </c>
+      <c r="AGE2" t="n">
+        <v>751451</v>
+      </c>
+      <c r="AGF2" t="n">
+        <v>666772</v>
+      </c>
+      <c r="AGG2" t="n">
+        <v>1079319</v>
+      </c>
+      <c r="AGH2" t="n">
+        <v>1189617</v>
+      </c>
+      <c r="AGI2" t="n">
+        <v>188809</v>
+      </c>
+      <c r="AGJ2" t="n">
+        <v>246611</v>
+      </c>
+      <c r="AGK2" t="n">
+        <v>12982</v>
+      </c>
+      <c r="AGL2" t="n">
+        <v>522709</v>
+      </c>
+      <c r="AGM2" t="n">
+        <v>341601</v>
+      </c>
+      <c r="AGN2" t="n">
+        <v>822720</v>
+      </c>
+      <c r="AGO2" t="n">
+        <v>528809</v>
+      </c>
+      <c r="AGP2" t="n">
+        <v>568721</v>
+      </c>
+      <c r="AGQ2" t="n">
+        <v>1008250</v>
+      </c>
+      <c r="AGR2" t="n">
+        <v>727224</v>
+      </c>
+      <c r="AGS2" t="n">
+        <v>141610</v>
+      </c>
+      <c r="AGT2" t="n">
+        <v>102126</v>
+      </c>
+      <c r="AGU2" t="n">
+        <v>1119907</v>
+      </c>
+      <c r="AGV2" t="n">
+        <v>970155</v>
+      </c>
+      <c r="AGW2" t="n">
+        <v>853787</v>
+      </c>
+      <c r="AGX2" t="n">
+        <v>340341</v>
+      </c>
+      <c r="AGY2" t="n">
+        <v>659971</v>
+      </c>
+      <c r="AGZ2" t="n">
+        <v>13397</v>
+      </c>
+      <c r="AHA2" t="n">
+        <v>551808</v>
+      </c>
+      <c r="AHB2" t="n">
+        <v>208790</v>
+      </c>
+      <c r="AHC2" t="n">
+        <v>448792</v>
+      </c>
+      <c r="AHD2" t="n">
+        <v>924447</v>
+      </c>
+      <c r="AHE2" t="n">
+        <v>8948</v>
+      </c>
+      <c r="AHF2" t="n">
+        <v>1230855</v>
+      </c>
+      <c r="AHG2" t="n">
+        <v>60771</v>
+      </c>
+      <c r="AHH2" t="n">
+        <v>947849</v>
+      </c>
+      <c r="AHI2" t="n">
+        <v>404685</v>
+      </c>
+      <c r="AHJ2" t="n">
+        <v>94091</v>
+      </c>
+      <c r="AHK2" t="n">
+        <v>784259</v>
+      </c>
+      <c r="AHL2" t="n">
+        <v>382384</v>
+      </c>
+      <c r="AHM2" t="n">
+        <v>648122</v>
+      </c>
+      <c r="AHN2" t="n">
+        <v>692259</v>
+      </c>
+      <c r="AHO2" t="n">
+        <v>607687</v>
+      </c>
+      <c r="AHP2" t="n">
+        <v>627625</v>
+      </c>
+      <c r="AHQ2" t="n">
+        <v>831351</v>
+      </c>
+      <c r="AHR2" t="n">
+        <v>667455</v>
+      </c>
+      <c r="AHS2" t="n">
+        <v>713337</v>
+      </c>
+      <c r="AHT2" t="n">
+        <v>27878</v>
+      </c>
+      <c r="AHU2" t="n">
+        <v>637486</v>
+      </c>
+      <c r="AHV2" t="n">
+        <v>120158</v>
+      </c>
+      <c r="AHW2" t="n">
+        <v>929425</v>
+      </c>
+      <c r="AHX2" t="n">
+        <v>360803</v>
+      </c>
+      <c r="AHY2" t="n">
+        <v>310718</v>
+      </c>
+      <c r="AHZ2" t="n">
+        <v>1107601</v>
+      </c>
+      <c r="AIA2" t="n">
+        <v>1032641</v>
+      </c>
+      <c r="AIB2" t="n">
+        <v>456000</v>
+      </c>
+      <c r="AIC2" t="n">
+        <v>965560</v>
+      </c>
+      <c r="AID2" t="n">
+        <v>681226</v>
+      </c>
+      <c r="AIE2" t="n">
+        <v>31696</v>
+      </c>
+      <c r="AIF2" t="n">
+        <v>505406</v>
+      </c>
+      <c r="AIG2" t="n">
+        <v>326854</v>
+      </c>
+      <c r="AIH2" t="n">
+        <v>832881</v>
+      </c>
+      <c r="AII2" t="n">
+        <v>1014828</v>
+      </c>
+      <c r="AIJ2" t="n">
+        <v>402739</v>
+      </c>
+      <c r="AIK2" t="n">
+        <v>270078</v>
+      </c>
+      <c r="AIL2" t="n">
+        <v>222705</v>
+      </c>
+      <c r="AIM2" t="n">
+        <v>1164729</v>
+      </c>
+      <c r="AIN2" t="n">
+        <v>1102253</v>
+      </c>
+      <c r="AIO2" t="n">
+        <v>802141</v>
+      </c>
+      <c r="AIP2" t="n">
+        <v>418395</v>
+      </c>
+      <c r="AIQ2" t="n">
+        <v>842330</v>
+      </c>
+      <c r="AIR2" t="n">
+        <v>781926</v>
+      </c>
+      <c r="AIS2" t="n">
+        <v>497230</v>
+      </c>
+      <c r="AIT2" t="n">
+        <v>515428</v>
+      </c>
+      <c r="AIU2" t="n">
+        <v>812991</v>
+      </c>
+      <c r="AIV2" t="n">
+        <v>586496</v>
+      </c>
+      <c r="AIW2" t="n">
+        <v>81042</v>
+      </c>
+      <c r="AIX2" t="n">
+        <v>459520</v>
+      </c>
+      <c r="AIY2" t="n">
+        <v>598765</v>
+      </c>
+      <c r="AIZ2" t="n">
+        <v>1102245</v>
+      </c>
+      <c r="AJA2" t="n">
+        <v>31733</v>
+      </c>
+      <c r="AJB2" t="n">
+        <v>756894</v>
+      </c>
+      <c r="AJC2" t="n">
+        <v>856894</v>
+      </c>
+      <c r="AJD2" t="n">
+        <v>523765</v>
+      </c>
+      <c r="AJE2" t="n">
+        <v>823355</v>
+      </c>
+      <c r="AJF2" t="n">
+        <v>1003607</v>
+      </c>
+      <c r="AJG2" t="n">
+        <v>525790</v>
+      </c>
+      <c r="AJH2" t="n">
+        <v>387749</v>
+      </c>
+      <c r="AJI2" t="n">
+        <v>253107</v>
+      </c>
+      <c r="AJJ2" t="n">
+        <v>643631</v>
+      </c>
+      <c r="AJK2" t="n">
+        <v>1012834</v>
+      </c>
+      <c r="AJL2" t="n">
+        <v>137732</v>
+      </c>
+      <c r="AJM2" t="n">
+        <v>500781</v>
+      </c>
+      <c r="AJN2" t="n">
+        <v>89899</v>
+      </c>
+      <c r="AJO2" t="n">
+        <v>558018</v>
+      </c>
+      <c r="AJP2" t="n">
+        <v>1219116</v>
+      </c>
+      <c r="AJQ2" t="n">
+        <v>50459</v>
+      </c>
+      <c r="AJR2" t="n">
+        <v>903018</v>
+      </c>
+      <c r="AJS2" t="n">
+        <v>457844</v>
+      </c>
+      <c r="AJT2" t="n">
+        <v>536978</v>
+      </c>
+      <c r="AJU2" t="n">
+        <v>993725</v>
+      </c>
+      <c r="AJV2" t="n">
+        <v>1089080</v>
+      </c>
+      <c r="AJW2" t="n">
+        <v>103083</v>
+      </c>
+      <c r="AJX2" t="n">
+        <v>390838</v>
+      </c>
+      <c r="AJY2" t="n">
+        <v>10570</v>
+      </c>
+      <c r="AJZ2" t="n">
+        <v>940567</v>
+      </c>
+      <c r="AKA2" t="n">
+        <v>730317</v>
+      </c>
+      <c r="AKB2" t="n">
+        <v>482020</v>
+      </c>
+      <c r="AKC2" t="n">
+        <v>899298</v>
+      </c>
+      <c r="AKD2" t="n">
+        <v>1076443</v>
+      </c>
+      <c r="AKE2" t="n">
+        <v>141465</v>
+      </c>
+      <c r="AKF2" t="n">
+        <v>581061</v>
+      </c>
+      <c r="AKG2" t="n">
+        <v>1148426</v>
+      </c>
+      <c r="AKH2" t="n">
+        <v>948046</v>
+      </c>
+      <c r="AKI2" t="n">
+        <v>751960</v>
+      </c>
+      <c r="AKJ2" t="n">
+        <v>1220670</v>
+      </c>
+      <c r="AKK2" t="n">
+        <v>106016</v>
+      </c>
+      <c r="AKL2" t="n">
+        <v>1041447</v>
+      </c>
+      <c r="AKM2" t="n">
+        <v>846553</v>
+      </c>
+      <c r="AKN2" t="n">
+        <v>683544</v>
+      </c>
+      <c r="AKO2" t="n">
+        <v>538046</v>
+      </c>
+      <c r="AKP2" t="n">
+        <v>851670</v>
+      </c>
+      <c r="AKQ2" t="n">
+        <v>927589</v>
+      </c>
+      <c r="AKR2" t="n">
+        <v>116733</v>
+      </c>
+      <c r="AKS2" t="n">
+        <v>1138197</v>
+      </c>
+      <c r="AKT2" t="n">
+        <v>563076</v>
+      </c>
+      <c r="AKU2" t="n">
+        <v>3324</v>
+      </c>
+      <c r="AKV2" t="n">
+        <v>989658</v>
+      </c>
+      <c r="AKW2" t="n">
+        <v>191752</v>
+      </c>
+      <c r="AKX2" t="n">
+        <v>1084435</v>
+      </c>
+      <c r="AKY2" t="n">
+        <v>1066483</v>
+      </c>
+      <c r="AKZ2" t="n">
+        <v>510330</v>
+      </c>
+      <c r="ALA2" t="n">
+        <v>879875</v>
+      </c>
+      <c r="ALB2" t="n">
+        <v>1092429</v>
+      </c>
+      <c r="ALC2" t="n">
+        <v>53257</v>
+      </c>
+      <c r="ALD2" t="n">
+        <v>440140</v>
+      </c>
+      <c r="ALE2" t="n">
+        <v>827665</v>
+      </c>
+      <c r="ALF2" t="n">
+        <v>417999</v>
+      </c>
+      <c r="ALG2" t="n">
+        <v>221969</v>
+      </c>
+      <c r="ALH2" t="n">
+        <v>624638</v>
+      </c>
+      <c r="ALI2" t="n">
+        <v>802552</v>
+      </c>
+      <c r="ALJ2" t="n">
+        <v>1051947</v>
+      </c>
+      <c r="ALK2" t="n">
+        <v>313221</v>
+      </c>
+      <c r="ALL2" t="n">
+        <v>1203161</v>
       </c>
     </row>
   </sheetData>
